--- a/data/แบบรายงานการคัดกรองและดูแลช่วยเหลือผู้สูงอายุกลุ่มเสี่ยง.xlsx
+++ b/data/แบบรายงานการคัดกรองและดูแลช่วยเหลือผู้สูงอายุกลุ่มเสี่ยง.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NextJSProjects\next16-mhc9-elderly\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0BF76209-CCF2-48CD-A582-06A3A046267B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE1B11B-4F2E-4A31-95C8-38E31535C06C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1366" uniqueCount="807">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1789" uniqueCount="807">
   <si>
     <t>ลำดับ/</t>
   </si>
@@ -3121,10 +3121,31 @@
     <xf numFmtId="0" fontId="14" fillId="8" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3143,31 +3164,15 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3183,16 +3188,11 @@
     <xf numFmtId="0" fontId="10" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="13" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3418,60 +3418,60 @@
   <sheetFormatPr defaultColWidth="12.59765625" defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="5.46484375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.06640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.46484375" customWidth="1"/>
     <col min="3" max="3" width="17.59765625" customWidth="1"/>
     <col min="4" max="4" width="75.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.6640625" customWidth="1"/>
     <col min="6" max="6" width="18.33203125" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="5.3984375" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.6640625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.46484375" customWidth="1"/>
     <col min="10" max="10" width="5.3984375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="10.46484375" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="5.3984375" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11.1328125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.265625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="6" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="5.3984375" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.19921875" customWidth="1"/>
+    <col min="15" max="15" width="7.3984375" customWidth="1"/>
+    <col min="16" max="16" width="7" customWidth="1"/>
     <col min="17" max="17" width="21.46484375" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="11.19921875" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="111.19921875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" ht="15">
-      <c r="A1" s="90" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="90" t="s">
+    <row r="1" spans="1:29" ht="21.4" customHeight="1">
+      <c r="A1" s="100" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="100" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="90" t="s">
+      <c r="C1" s="100" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="90" t="s">
+      <c r="D1" s="100" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="92" t="s">
+      <c r="E1" s="101" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="93" t="s">
+      <c r="F1" s="102" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="94"/>
-      <c r="H1" s="95"/>
-      <c r="I1" s="101" t="s">
+      <c r="G1" s="103"/>
+      <c r="H1" s="104"/>
+      <c r="I1" s="110" t="s">
         <v>6</v>
       </c>
-      <c r="J1" s="102"/>
-      <c r="K1" s="102"/>
-      <c r="L1" s="102"/>
-      <c r="M1" s="102"/>
-      <c r="N1" s="102"/>
-      <c r="O1" s="103"/>
-      <c r="P1" s="104" t="s">
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="92"/>
+      <c r="P1" s="90" t="s">
         <v>7</v>
       </c>
-      <c r="Q1" s="102"/>
-      <c r="R1" s="103"/>
+      <c r="Q1" s="91"/>
+      <c r="R1" s="92"/>
       <c r="S1" s="2"/>
       <c r="T1" s="2"/>
       <c r="U1" s="2"/>
@@ -3484,37 +3484,37 @@
       <c r="AB1" s="1"/>
       <c r="AC1" s="1"/>
     </row>
-    <row r="2" spans="1:29">
-      <c r="A2" s="91"/>
-      <c r="B2" s="91"/>
-      <c r="C2" s="91"/>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="96"/>
-      <c r="G2" s="97"/>
-      <c r="H2" s="98"/>
-      <c r="I2" s="105" t="s">
+    <row r="2" spans="1:29" ht="21.4" customHeight="1">
+      <c r="A2" s="98"/>
+      <c r="B2" s="98"/>
+      <c r="C2" s="98"/>
+      <c r="D2" s="98"/>
+      <c r="E2" s="98"/>
+      <c r="F2" s="105"/>
+      <c r="G2" s="106"/>
+      <c r="H2" s="107"/>
+      <c r="I2" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="J2" s="107" t="s">
+      <c r="J2" s="95" t="s">
         <v>9</v>
       </c>
-      <c r="K2" s="103"/>
-      <c r="L2" s="108" t="s">
+      <c r="K2" s="92"/>
+      <c r="L2" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="M2" s="102"/>
-      <c r="N2" s="109" t="s">
+      <c r="M2" s="91"/>
+      <c r="N2" s="97" t="s">
         <v>11</v>
       </c>
-      <c r="O2" s="99" t="s">
+      <c r="O2" s="108" t="s">
         <v>12</v>
       </c>
-      <c r="P2" s="110" t="s">
+      <c r="P2" s="99" t="s">
         <v>13</v>
       </c>
-      <c r="Q2" s="102"/>
-      <c r="R2" s="103"/>
+      <c r="Q2" s="91"/>
+      <c r="R2" s="92"/>
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
@@ -3527,12 +3527,12 @@
       <c r="AB2" s="1"/>
       <c r="AC2" s="1"/>
     </row>
-    <row r="3" spans="1:29" ht="61.9">
-      <c r="A3" s="91"/>
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
+    <row r="3" spans="1:29" ht="82.5">
+      <c r="A3" s="98"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
       <c r="F3" s="5" t="s">
         <v>14</v>
       </c>
@@ -3542,7 +3542,7 @@
       <c r="H3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="I3" s="106"/>
+      <c r="I3" s="94"/>
       <c r="J3" s="3" t="s">
         <v>15</v>
       </c>
@@ -3555,8 +3555,8 @@
       <c r="M3" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="N3" s="91"/>
-      <c r="O3" s="100"/>
+      <c r="N3" s="98"/>
+      <c r="O3" s="109"/>
       <c r="P3" s="9" t="s">
         <v>15</v>
       </c>
@@ -3623,7 +3623,9 @@
       <c r="A5" s="74">
         <v>2</v>
       </c>
-      <c r="B5" s="76"/>
+      <c r="B5" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C5" s="75" t="s">
         <v>22</v>
       </c>
@@ -3682,7 +3684,9 @@
       <c r="A6" s="74">
         <v>3</v>
       </c>
-      <c r="B6" s="76"/>
+      <c r="B6" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C6" s="75" t="s">
         <v>22</v>
       </c>
@@ -3741,7 +3745,9 @@
       <c r="A7" s="74">
         <v>4</v>
       </c>
-      <c r="B7" s="76"/>
+      <c r="B7" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C7" s="75" t="s">
         <v>22</v>
       </c>
@@ -3790,7 +3796,9 @@
       <c r="A8" s="74">
         <v>5</v>
       </c>
-      <c r="B8" s="76"/>
+      <c r="B8" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C8" s="75" t="s">
         <v>22</v>
       </c>
@@ -3849,7 +3857,9 @@
       <c r="A9" s="74">
         <v>6</v>
       </c>
-      <c r="B9" s="76"/>
+      <c r="B9" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C9" s="75" t="s">
         <v>22</v>
       </c>
@@ -3908,7 +3918,9 @@
       <c r="A10" s="74">
         <v>7</v>
       </c>
-      <c r="B10" s="76"/>
+      <c r="B10" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C10" s="75" t="s">
         <v>22</v>
       </c>
@@ -3955,7 +3967,9 @@
       <c r="A11" s="74">
         <v>8</v>
       </c>
-      <c r="B11" s="76"/>
+      <c r="B11" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C11" s="75" t="s">
         <v>22</v>
       </c>
@@ -4014,7 +4028,9 @@
       <c r="A12" s="74">
         <v>9</v>
       </c>
-      <c r="B12" s="76"/>
+      <c r="B12" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C12" s="75" t="s">
         <v>31</v>
       </c>
@@ -4053,7 +4069,9 @@
       <c r="A13" s="74">
         <v>10</v>
       </c>
-      <c r="B13" s="76"/>
+      <c r="B13" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C13" s="75" t="s">
         <v>31</v>
       </c>
@@ -4098,7 +4116,9 @@
       <c r="A14" s="74">
         <v>11</v>
       </c>
-      <c r="B14" s="76"/>
+      <c r="B14" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C14" s="75" t="s">
         <v>31</v>
       </c>
@@ -4145,7 +4165,9 @@
       <c r="A15" s="74">
         <v>12</v>
       </c>
-      <c r="B15" s="76"/>
+      <c r="B15" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C15" s="75" t="s">
         <v>31</v>
       </c>
@@ -4204,7 +4226,9 @@
       <c r="A16" s="74">
         <v>13</v>
       </c>
-      <c r="B16" s="76"/>
+      <c r="B16" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C16" s="75" t="s">
         <v>31</v>
       </c>
@@ -4251,7 +4275,9 @@
       <c r="A17" s="74">
         <v>14</v>
       </c>
-      <c r="B17" s="76"/>
+      <c r="B17" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C17" s="75" t="s">
         <v>31</v>
       </c>
@@ -4296,7 +4322,9 @@
       <c r="A18" s="74">
         <v>15</v>
       </c>
-      <c r="B18" s="76"/>
+      <c r="B18" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C18" s="75" t="s">
         <v>31</v>
       </c>
@@ -4355,7 +4383,9 @@
       <c r="A19" s="74">
         <v>16</v>
       </c>
-      <c r="B19" s="76"/>
+      <c r="B19" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C19" s="75" t="s">
         <v>39</v>
       </c>
@@ -4414,7 +4444,9 @@
       <c r="A20" s="74">
         <v>17</v>
       </c>
-      <c r="B20" s="76"/>
+      <c r="B20" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C20" s="75" t="s">
         <v>39</v>
       </c>
@@ -4473,7 +4505,9 @@
       <c r="A21" s="74">
         <v>18</v>
       </c>
-      <c r="B21" s="76"/>
+      <c r="B21" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C21" s="75" t="s">
         <v>39</v>
       </c>
@@ -4532,7 +4566,9 @@
       <c r="A22" s="74">
         <v>19</v>
       </c>
-      <c r="B22" s="76"/>
+      <c r="B22" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C22" s="75" t="s">
         <v>39</v>
       </c>
@@ -4591,7 +4627,9 @@
       <c r="A23" s="74">
         <v>20</v>
       </c>
-      <c r="B23" s="76"/>
+      <c r="B23" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C23" s="75" t="s">
         <v>39</v>
       </c>
@@ -4636,7 +4674,9 @@
       <c r="A24" s="74">
         <v>21</v>
       </c>
-      <c r="B24" s="76"/>
+      <c r="B24" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C24" s="75" t="s">
         <v>39</v>
       </c>
@@ -4695,7 +4735,9 @@
       <c r="A25" s="74">
         <v>22</v>
       </c>
-      <c r="B25" s="76"/>
+      <c r="B25" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C25" s="75" t="s">
         <v>39</v>
       </c>
@@ -4754,7 +4796,9 @@
       <c r="A26" s="74">
         <v>23</v>
       </c>
-      <c r="B26" s="76"/>
+      <c r="B26" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C26" s="75" t="s">
         <v>39</v>
       </c>
@@ -4811,7 +4855,9 @@
       <c r="A27" s="74">
         <v>24</v>
       </c>
-      <c r="B27" s="76"/>
+      <c r="B27" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C27" s="75" t="s">
         <v>39</v>
       </c>
@@ -4870,7 +4916,9 @@
       <c r="A28" s="74">
         <v>25</v>
       </c>
-      <c r="B28" s="76"/>
+      <c r="B28" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C28" s="75" t="s">
         <v>39</v>
       </c>
@@ -4929,7 +4977,9 @@
       <c r="A29" s="74">
         <v>26</v>
       </c>
-      <c r="B29" s="76"/>
+      <c r="B29" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C29" s="75" t="s">
         <v>39</v>
       </c>
@@ -4974,7 +5024,9 @@
       <c r="A30" s="74">
         <v>27</v>
       </c>
-      <c r="B30" s="76"/>
+      <c r="B30" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C30" s="75" t="s">
         <v>51</v>
       </c>
@@ -5013,7 +5065,9 @@
       <c r="A31" s="74">
         <v>28</v>
       </c>
-      <c r="B31" s="76"/>
+      <c r="B31" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C31" s="75" t="s">
         <v>51</v>
       </c>
@@ -5052,7 +5106,9 @@
       <c r="A32" s="74">
         <v>29</v>
       </c>
-      <c r="B32" s="76"/>
+      <c r="B32" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C32" s="75" t="s">
         <v>51</v>
       </c>
@@ -5097,7 +5153,9 @@
       <c r="A33" s="74">
         <v>30</v>
       </c>
-      <c r="B33" s="76"/>
+      <c r="B33" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C33" s="75" t="s">
         <v>51</v>
       </c>
@@ -5142,7 +5200,9 @@
       <c r="A34" s="74">
         <v>31</v>
       </c>
-      <c r="B34" s="76"/>
+      <c r="B34" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C34" s="75" t="s">
         <v>51</v>
       </c>
@@ -5201,7 +5261,9 @@
       <c r="A35" s="74">
         <v>32</v>
       </c>
-      <c r="B35" s="76"/>
+      <c r="B35" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C35" s="75" t="s">
         <v>51</v>
       </c>
@@ -5246,7 +5308,9 @@
       <c r="A36" s="74">
         <v>33</v>
       </c>
-      <c r="B36" s="76"/>
+      <c r="B36" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C36" s="75" t="s">
         <v>51</v>
       </c>
@@ -5291,7 +5355,9 @@
       <c r="A37" s="74">
         <v>34</v>
       </c>
-      <c r="B37" s="76"/>
+      <c r="B37" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C37" s="75" t="s">
         <v>51</v>
       </c>
@@ -5336,7 +5402,9 @@
       <c r="A38" s="74">
         <v>35</v>
       </c>
-      <c r="B38" s="76"/>
+      <c r="B38" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C38" s="75" t="s">
         <v>51</v>
       </c>
@@ -5377,7 +5445,9 @@
       <c r="A39" s="74">
         <v>36</v>
       </c>
-      <c r="B39" s="76"/>
+      <c r="B39" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C39" s="75" t="s">
         <v>51</v>
       </c>
@@ -5436,7 +5506,9 @@
       <c r="A40" s="74">
         <v>37</v>
       </c>
-      <c r="B40" s="76"/>
+      <c r="B40" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C40" s="75" t="s">
         <v>51</v>
       </c>
@@ -5481,7 +5553,9 @@
       <c r="A41" s="74">
         <v>38</v>
       </c>
-      <c r="B41" s="76"/>
+      <c r="B41" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C41" s="75" t="s">
         <v>51</v>
       </c>
@@ -5526,7 +5600,9 @@
       <c r="A42" s="74">
         <v>39</v>
       </c>
-      <c r="B42" s="76"/>
+      <c r="B42" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C42" s="75" t="s">
         <v>51</v>
       </c>
@@ -5571,7 +5647,9 @@
       <c r="A43" s="74">
         <v>40</v>
       </c>
-      <c r="B43" s="76"/>
+      <c r="B43" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C43" s="75" t="s">
         <v>51</v>
       </c>
@@ -5616,7 +5694,9 @@
       <c r="A44" s="74">
         <v>41</v>
       </c>
-      <c r="B44" s="76"/>
+      <c r="B44" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C44" s="75" t="s">
         <v>51</v>
       </c>
@@ -5661,7 +5741,9 @@
       <c r="A45" s="74">
         <v>42</v>
       </c>
-      <c r="B45" s="76"/>
+      <c r="B45" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C45" s="75" t="s">
         <v>51</v>
       </c>
@@ -5706,7 +5788,9 @@
       <c r="A46" s="74">
         <v>43</v>
       </c>
-      <c r="B46" s="76"/>
+      <c r="B46" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C46" s="75" t="s">
         <v>51</v>
       </c>
@@ -5751,7 +5835,9 @@
       <c r="A47" s="74">
         <v>44</v>
       </c>
-      <c r="B47" s="76"/>
+      <c r="B47" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C47" s="75" t="s">
         <v>51</v>
       </c>
@@ -5810,7 +5896,9 @@
       <c r="A48" s="74">
         <v>45</v>
       </c>
-      <c r="B48" s="76"/>
+      <c r="B48" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C48" s="75" t="s">
         <v>51</v>
       </c>
@@ -5855,7 +5943,9 @@
       <c r="A49" s="74">
         <v>46</v>
       </c>
-      <c r="B49" s="76"/>
+      <c r="B49" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C49" s="75" t="s">
         <v>71</v>
       </c>
@@ -5902,7 +5992,9 @@
       <c r="A50" s="74">
         <v>47</v>
       </c>
-      <c r="B50" s="76"/>
+      <c r="B50" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C50" s="75" t="s">
         <v>71</v>
       </c>
@@ -5961,7 +6053,9 @@
       <c r="A51" s="74">
         <v>48</v>
       </c>
-      <c r="B51" s="76"/>
+      <c r="B51" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C51" s="75" t="s">
         <v>71</v>
       </c>
@@ -6006,7 +6100,9 @@
       <c r="A52" s="74">
         <v>49</v>
       </c>
-      <c r="B52" s="76"/>
+      <c r="B52" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C52" s="75" t="s">
         <v>71</v>
       </c>
@@ -6051,7 +6147,9 @@
       <c r="A53" s="74">
         <v>50</v>
       </c>
-      <c r="B53" s="76"/>
+      <c r="B53" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C53" s="75" t="s">
         <v>71</v>
       </c>
@@ -6110,7 +6208,9 @@
       <c r="A54" s="74">
         <v>51</v>
       </c>
-      <c r="B54" s="76"/>
+      <c r="B54" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C54" s="75" t="s">
         <v>71</v>
       </c>
@@ -6169,7 +6269,9 @@
       <c r="A55" s="74">
         <v>52</v>
       </c>
-      <c r="B55" s="76"/>
+      <c r="B55" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C55" s="75" t="s">
         <v>71</v>
       </c>
@@ -6216,7 +6318,9 @@
       <c r="A56" s="74">
         <v>53</v>
       </c>
-      <c r="B56" s="76"/>
+      <c r="B56" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C56" s="75" t="s">
         <v>71</v>
       </c>
@@ -6261,7 +6365,9 @@
       <c r="A57" s="74">
         <v>54</v>
       </c>
-      <c r="B57" s="76"/>
+      <c r="B57" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C57" s="75" t="s">
         <v>80</v>
       </c>
@@ -6306,7 +6412,9 @@
       <c r="A58" s="74">
         <v>55</v>
       </c>
-      <c r="B58" s="76"/>
+      <c r="B58" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C58" s="75" t="s">
         <v>80</v>
       </c>
@@ -6351,7 +6459,9 @@
       <c r="A59" s="74">
         <v>56</v>
       </c>
-      <c r="B59" s="76"/>
+      <c r="B59" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C59" s="75" t="s">
         <v>80</v>
       </c>
@@ -6396,7 +6506,9 @@
       <c r="A60" s="74">
         <v>57</v>
       </c>
-      <c r="B60" s="76"/>
+      <c r="B60" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C60" s="75" t="s">
         <v>80</v>
       </c>
@@ -6441,7 +6553,9 @@
       <c r="A61" s="74">
         <v>58</v>
       </c>
-      <c r="B61" s="76"/>
+      <c r="B61" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C61" s="75" t="s">
         <v>80</v>
       </c>
@@ -6486,7 +6600,9 @@
       <c r="A62" s="74">
         <v>59</v>
       </c>
-      <c r="B62" s="76"/>
+      <c r="B62" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C62" s="75" t="s">
         <v>80</v>
       </c>
@@ -6527,7 +6643,9 @@
       <c r="A63" s="74">
         <v>60</v>
       </c>
-      <c r="B63" s="76"/>
+      <c r="B63" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C63" s="75" t="s">
         <v>80</v>
       </c>
@@ -6572,7 +6690,9 @@
       <c r="A64" s="74">
         <v>61</v>
       </c>
-      <c r="B64" s="76"/>
+      <c r="B64" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C64" s="75" t="s">
         <v>80</v>
       </c>
@@ -6617,7 +6737,9 @@
       <c r="A65" s="74">
         <v>62</v>
       </c>
-      <c r="B65" s="76"/>
+      <c r="B65" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C65" s="75" t="s">
         <v>80</v>
       </c>
@@ -6662,7 +6784,9 @@
       <c r="A66" s="74">
         <v>63</v>
       </c>
-      <c r="B66" s="76"/>
+      <c r="B66" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C66" s="75" t="s">
         <v>80</v>
       </c>
@@ -6721,7 +6845,9 @@
       <c r="A67" s="74">
         <v>64</v>
       </c>
-      <c r="B67" s="76"/>
+      <c r="B67" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C67" s="75" t="s">
         <v>80</v>
       </c>
@@ -6766,7 +6892,9 @@
       <c r="A68" s="74">
         <v>65</v>
       </c>
-      <c r="B68" s="76"/>
+      <c r="B68" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C68" s="75" t="s">
         <v>80</v>
       </c>
@@ -6811,7 +6939,9 @@
       <c r="A69" s="74">
         <v>66</v>
       </c>
-      <c r="B69" s="76"/>
+      <c r="B69" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C69" s="75" t="s">
         <v>80</v>
       </c>
@@ -6870,7 +7000,9 @@
       <c r="A70" s="74">
         <v>67</v>
       </c>
-      <c r="B70" s="76"/>
+      <c r="B70" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C70" s="75" t="s">
         <v>94</v>
       </c>
@@ -6915,7 +7047,9 @@
       <c r="A71" s="74">
         <v>68</v>
       </c>
-      <c r="B71" s="76"/>
+      <c r="B71" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C71" s="75" t="s">
         <v>94</v>
       </c>
@@ -6960,7 +7094,9 @@
       <c r="A72" s="74">
         <v>69</v>
       </c>
-      <c r="B72" s="76"/>
+      <c r="B72" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C72" s="75" t="s">
         <v>94</v>
       </c>
@@ -7005,7 +7141,9 @@
       <c r="A73" s="74">
         <v>70</v>
       </c>
-      <c r="B73" s="76"/>
+      <c r="B73" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C73" s="75" t="s">
         <v>94</v>
       </c>
@@ -7050,7 +7188,9 @@
       <c r="A74" s="74">
         <v>71</v>
       </c>
-      <c r="B74" s="76"/>
+      <c r="B74" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C74" s="75" t="s">
         <v>94</v>
       </c>
@@ -7095,7 +7235,9 @@
       <c r="A75" s="74">
         <v>72</v>
       </c>
-      <c r="B75" s="76"/>
+      <c r="B75" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C75" s="75" t="s">
         <v>94</v>
       </c>
@@ -7140,7 +7282,9 @@
       <c r="A76" s="74">
         <v>73</v>
       </c>
-      <c r="B76" s="76"/>
+      <c r="B76" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C76" s="75" t="s">
         <v>94</v>
       </c>
@@ -7185,7 +7329,9 @@
       <c r="A77" s="74">
         <v>74</v>
       </c>
-      <c r="B77" s="76"/>
+      <c r="B77" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C77" s="75" t="s">
         <v>94</v>
       </c>
@@ -7230,7 +7376,9 @@
       <c r="A78" s="74">
         <v>75</v>
       </c>
-      <c r="B78" s="76"/>
+      <c r="B78" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C78" s="75" t="s">
         <v>94</v>
       </c>
@@ -7275,7 +7423,9 @@
       <c r="A79" s="74">
         <v>76</v>
       </c>
-      <c r="B79" s="76"/>
+      <c r="B79" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C79" s="75" t="s">
         <v>94</v>
       </c>
@@ -7320,7 +7470,9 @@
       <c r="A80" s="74">
         <v>77</v>
       </c>
-      <c r="B80" s="76"/>
+      <c r="B80" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C80" s="75" t="s">
         <v>94</v>
       </c>
@@ -7381,7 +7533,9 @@
       <c r="A81" s="74">
         <v>78</v>
       </c>
-      <c r="B81" s="76"/>
+      <c r="B81" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C81" s="75" t="s">
         <v>94</v>
       </c>
@@ -7426,7 +7580,9 @@
       <c r="A82" s="74">
         <v>79</v>
       </c>
-      <c r="B82" s="76"/>
+      <c r="B82" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C82" s="75" t="s">
         <v>94</v>
       </c>
@@ -7485,7 +7641,9 @@
       <c r="A83" s="74">
         <v>80</v>
       </c>
-      <c r="B83" s="76"/>
+      <c r="B83" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C83" s="75" t="s">
         <v>94</v>
       </c>
@@ -7530,7 +7688,9 @@
       <c r="A84" s="74">
         <v>81</v>
       </c>
-      <c r="B84" s="76"/>
+      <c r="B84" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C84" s="75" t="s">
         <v>94</v>
       </c>
@@ -7587,7 +7747,9 @@
       <c r="A85" s="74">
         <v>82</v>
       </c>
-      <c r="B85" s="76"/>
+      <c r="B85" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C85" s="75" t="s">
         <v>94</v>
       </c>
@@ -7646,7 +7808,9 @@
       <c r="A86" s="74">
         <v>83</v>
       </c>
-      <c r="B86" s="76"/>
+      <c r="B86" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C86" s="75" t="s">
         <v>94</v>
       </c>
@@ -7691,7 +7855,9 @@
       <c r="A87" s="74">
         <v>84</v>
       </c>
-      <c r="B87" s="76"/>
+      <c r="B87" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C87" s="75" t="s">
         <v>94</v>
       </c>
@@ -7748,7 +7914,9 @@
       <c r="A88" s="74">
         <v>85</v>
       </c>
-      <c r="B88" s="76"/>
+      <c r="B88" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C88" s="75" t="s">
         <v>94</v>
       </c>
@@ -7793,7 +7961,9 @@
       <c r="A89" s="74">
         <v>86</v>
       </c>
-      <c r="B89" s="76"/>
+      <c r="B89" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C89" s="75" t="s">
         <v>115</v>
       </c>
@@ -7852,7 +8022,9 @@
       <c r="A90" s="74">
         <v>87</v>
       </c>
-      <c r="B90" s="76"/>
+      <c r="B90" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C90" s="75" t="s">
         <v>115</v>
       </c>
@@ -7897,7 +8069,9 @@
       <c r="A91" s="74">
         <v>88</v>
       </c>
-      <c r="B91" s="76"/>
+      <c r="B91" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C91" s="75" t="s">
         <v>115</v>
       </c>
@@ -7956,7 +8130,9 @@
       <c r="A92" s="74">
         <v>89</v>
       </c>
-      <c r="B92" s="76"/>
+      <c r="B92" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C92" s="75" t="s">
         <v>115</v>
       </c>
@@ -7997,7 +8173,9 @@
       <c r="A93" s="74">
         <v>90</v>
       </c>
-      <c r="B93" s="76"/>
+      <c r="B93" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C93" s="75" t="s">
         <v>115</v>
       </c>
@@ -8054,7 +8232,9 @@
       <c r="A94" s="74">
         <v>91</v>
       </c>
-      <c r="B94" s="76"/>
+      <c r="B94" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C94" s="75" t="s">
         <v>121</v>
       </c>
@@ -8099,7 +8279,9 @@
       <c r="A95" s="74">
         <v>92</v>
       </c>
-      <c r="B95" s="76"/>
+      <c r="B95" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C95" s="75" t="s">
         <v>121</v>
       </c>
@@ -8140,7 +8322,9 @@
       <c r="A96" s="74">
         <v>93</v>
       </c>
-      <c r="B96" s="76"/>
+      <c r="B96" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C96" s="75" t="s">
         <v>121</v>
       </c>
@@ -8199,7 +8383,9 @@
       <c r="A97" s="74">
         <v>94</v>
       </c>
-      <c r="B97" s="76"/>
+      <c r="B97" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C97" s="75" t="s">
         <v>121</v>
       </c>
@@ -8258,7 +8444,9 @@
       <c r="A98" s="74">
         <v>95</v>
       </c>
-      <c r="B98" s="76"/>
+      <c r="B98" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C98" s="75" t="s">
         <v>121</v>
       </c>
@@ -8303,7 +8491,9 @@
       <c r="A99" s="74">
         <v>96</v>
       </c>
-      <c r="B99" s="76"/>
+      <c r="B99" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C99" s="75" t="s">
         <v>121</v>
       </c>
@@ -8362,7 +8552,9 @@
       <c r="A100" s="74">
         <v>97</v>
       </c>
-      <c r="B100" s="76"/>
+      <c r="B100" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C100" s="75" t="s">
         <v>121</v>
       </c>
@@ -8407,7 +8599,9 @@
       <c r="A101" s="74">
         <v>98</v>
       </c>
-      <c r="B101" s="76"/>
+      <c r="B101" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C101" s="75" t="s">
         <v>121</v>
       </c>
@@ -8452,7 +8646,9 @@
       <c r="A102" s="74">
         <v>99</v>
       </c>
-      <c r="B102" s="76"/>
+      <c r="B102" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C102" s="75" t="s">
         <v>121</v>
       </c>
@@ -8497,7 +8693,9 @@
       <c r="A103" s="74">
         <v>100</v>
       </c>
-      <c r="B103" s="76"/>
+      <c r="B103" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C103" s="75" t="s">
         <v>121</v>
       </c>
@@ -8542,7 +8740,9 @@
       <c r="A104" s="74">
         <v>101</v>
       </c>
-      <c r="B104" s="76"/>
+      <c r="B104" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C104" s="75" t="s">
         <v>121</v>
       </c>
@@ -8601,7 +8801,9 @@
       <c r="A105" s="74">
         <v>102</v>
       </c>
-      <c r="B105" s="76"/>
+      <c r="B105" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C105" s="75" t="s">
         <v>121</v>
       </c>
@@ -8646,7 +8848,9 @@
       <c r="A106" s="74">
         <v>103</v>
       </c>
-      <c r="B106" s="76"/>
+      <c r="B106" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C106" s="75" t="s">
         <v>121</v>
       </c>
@@ -8687,7 +8891,9 @@
       <c r="A107" s="74">
         <v>104</v>
       </c>
-      <c r="B107" s="76"/>
+      <c r="B107" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C107" s="75" t="s">
         <v>121</v>
       </c>
@@ -8744,7 +8950,9 @@
       <c r="A108" s="74">
         <v>105</v>
       </c>
-      <c r="B108" s="76"/>
+      <c r="B108" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C108" s="75" t="s">
         <v>135</v>
       </c>
@@ -8801,7 +9009,9 @@
       <c r="A109" s="74">
         <v>106</v>
       </c>
-      <c r="B109" s="76"/>
+      <c r="B109" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C109" s="75" t="s">
         <v>135</v>
       </c>
@@ -8846,7 +9056,9 @@
       <c r="A110" s="74">
         <v>107</v>
       </c>
-      <c r="B110" s="76"/>
+      <c r="B110" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C110" s="75" t="s">
         <v>135</v>
       </c>
@@ -8891,7 +9103,9 @@
       <c r="A111" s="74">
         <v>108</v>
       </c>
-      <c r="B111" s="76"/>
+      <c r="B111" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C111" s="75" t="s">
         <v>135</v>
       </c>
@@ -8936,7 +9150,9 @@
       <c r="A112" s="74">
         <v>109</v>
       </c>
-      <c r="B112" s="76"/>
+      <c r="B112" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C112" s="75" t="s">
         <v>140</v>
       </c>
@@ -8981,7 +9197,9 @@
       <c r="A113" s="74">
         <v>110</v>
       </c>
-      <c r="B113" s="76"/>
+      <c r="B113" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C113" s="75" t="s">
         <v>140</v>
       </c>
@@ -9026,7 +9244,9 @@
       <c r="A114" s="74">
         <v>111</v>
       </c>
-      <c r="B114" s="76"/>
+      <c r="B114" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C114" s="75" t="s">
         <v>140</v>
       </c>
@@ -9071,7 +9291,9 @@
       <c r="A115" s="74">
         <v>112</v>
       </c>
-      <c r="B115" s="76"/>
+      <c r="B115" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C115" s="75" t="s">
         <v>140</v>
       </c>
@@ -9116,7 +9338,9 @@
       <c r="A116" s="74">
         <v>113</v>
       </c>
-      <c r="B116" s="76"/>
+      <c r="B116" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C116" s="75" t="s">
         <v>140</v>
       </c>
@@ -9161,7 +9385,9 @@
       <c r="A117" s="74">
         <v>114</v>
       </c>
-      <c r="B117" s="76"/>
+      <c r="B117" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C117" s="75" t="s">
         <v>140</v>
       </c>
@@ -9202,7 +9428,9 @@
       <c r="A118" s="74">
         <v>115</v>
       </c>
-      <c r="B118" s="76"/>
+      <c r="B118" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C118" s="75" t="s">
         <v>140</v>
       </c>
@@ -9261,7 +9489,9 @@
       <c r="A119" s="74">
         <v>116</v>
       </c>
-      <c r="B119" s="76"/>
+      <c r="B119" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C119" s="75" t="s">
         <v>140</v>
       </c>
@@ -9306,7 +9536,9 @@
       <c r="A120" s="74">
         <v>117</v>
       </c>
-      <c r="B120" s="76"/>
+      <c r="B120" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C120" s="75" t="s">
         <v>140</v>
       </c>
@@ -9351,7 +9583,9 @@
       <c r="A121" s="74">
         <v>118</v>
       </c>
-      <c r="B121" s="76"/>
+      <c r="B121" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C121" s="75" t="s">
         <v>140</v>
       </c>
@@ -9396,7 +9630,9 @@
       <c r="A122" s="74">
         <v>119</v>
       </c>
-      <c r="B122" s="76"/>
+      <c r="B122" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C122" s="75" t="s">
         <v>140</v>
       </c>
@@ -9441,7 +9677,9 @@
       <c r="A123" s="74">
         <v>120</v>
       </c>
-      <c r="B123" s="76"/>
+      <c r="B123" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C123" s="75" t="s">
         <v>140</v>
       </c>
@@ -9500,7 +9738,9 @@
       <c r="A124" s="74">
         <v>121</v>
       </c>
-      <c r="B124" s="76"/>
+      <c r="B124" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C124" s="75" t="s">
         <v>140</v>
       </c>
@@ -9545,7 +9785,9 @@
       <c r="A125" s="74">
         <v>122</v>
       </c>
-      <c r="B125" s="76"/>
+      <c r="B125" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C125" s="75" t="s">
         <v>153</v>
       </c>
@@ -9586,7 +9828,9 @@
       <c r="A126" s="74">
         <v>123</v>
       </c>
-      <c r="B126" s="76"/>
+      <c r="B126" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C126" s="75" t="s">
         <v>153</v>
       </c>
@@ -9625,7 +9869,9 @@
       <c r="A127" s="74">
         <v>124</v>
       </c>
-      <c r="B127" s="76"/>
+      <c r="B127" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C127" s="75" t="s">
         <v>153</v>
       </c>
@@ -9664,7 +9910,9 @@
       <c r="A128" s="74">
         <v>125</v>
       </c>
-      <c r="B128" s="76"/>
+      <c r="B128" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C128" s="75" t="s">
         <v>153</v>
       </c>
@@ -9709,7 +9957,9 @@
       <c r="A129" s="74">
         <v>126</v>
       </c>
-      <c r="B129" s="76"/>
+      <c r="B129" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C129" s="75" t="s">
         <v>153</v>
       </c>
@@ -9754,7 +10004,9 @@
       <c r="A130" s="74">
         <v>127</v>
       </c>
-      <c r="B130" s="76"/>
+      <c r="B130" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C130" s="75" t="s">
         <v>153</v>
       </c>
@@ -9799,7 +10051,9 @@
       <c r="A131" s="74">
         <v>128</v>
       </c>
-      <c r="B131" s="76"/>
+      <c r="B131" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C131" s="75" t="s">
         <v>153</v>
       </c>
@@ -9844,7 +10098,9 @@
       <c r="A132" s="74">
         <v>129</v>
       </c>
-      <c r="B132" s="76"/>
+      <c r="B132" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C132" s="75" t="s">
         <v>153</v>
       </c>
@@ -9889,7 +10145,9 @@
       <c r="A133" s="74">
         <v>130</v>
       </c>
-      <c r="B133" s="76"/>
+      <c r="B133" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C133" s="75" t="s">
         <v>153</v>
       </c>
@@ -9934,7 +10192,9 @@
       <c r="A134" s="74">
         <v>131</v>
       </c>
-      <c r="B134" s="76"/>
+      <c r="B134" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C134" s="75" t="s">
         <v>153</v>
       </c>
@@ -9979,7 +10239,9 @@
       <c r="A135" s="74">
         <v>132</v>
       </c>
-      <c r="B135" s="76"/>
+      <c r="B135" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C135" s="75" t="s">
         <v>153</v>
       </c>
@@ -10038,7 +10300,9 @@
       <c r="A136" s="74">
         <v>133</v>
       </c>
-      <c r="B136" s="76"/>
+      <c r="B136" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C136" s="75" t="s">
         <v>153</v>
       </c>
@@ -10083,7 +10347,9 @@
       <c r="A137" s="74">
         <v>134</v>
       </c>
-      <c r="B137" s="76"/>
+      <c r="B137" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C137" s="75" t="s">
         <v>153</v>
       </c>
@@ -10128,7 +10394,9 @@
       <c r="A138" s="74">
         <v>135</v>
       </c>
-      <c r="B138" s="76"/>
+      <c r="B138" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C138" s="75" t="s">
         <v>153</v>
       </c>
@@ -10173,7 +10441,9 @@
       <c r="A139" s="74">
         <v>136</v>
       </c>
-      <c r="B139" s="76"/>
+      <c r="B139" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C139" s="75" t="s">
         <v>153</v>
       </c>
@@ -10218,7 +10488,9 @@
       <c r="A140" s="74">
         <v>137</v>
       </c>
-      <c r="B140" s="76"/>
+      <c r="B140" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C140" s="75" t="s">
         <v>153</v>
       </c>
@@ -10263,7 +10535,9 @@
       <c r="A141" s="74">
         <v>138</v>
       </c>
-      <c r="B141" s="76"/>
+      <c r="B141" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C141" s="75" t="s">
         <v>153</v>
       </c>
@@ -10308,7 +10582,9 @@
       <c r="A142" s="74">
         <v>139</v>
       </c>
-      <c r="B142" s="76"/>
+      <c r="B142" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C142" s="75" t="s">
         <v>153</v>
       </c>
@@ -10353,7 +10629,9 @@
       <c r="A143" s="74">
         <v>140</v>
       </c>
-      <c r="B143" s="76"/>
+      <c r="B143" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C143" s="75" t="s">
         <v>153</v>
       </c>
@@ -10398,7 +10676,9 @@
       <c r="A144" s="74">
         <v>141</v>
       </c>
-      <c r="B144" s="76"/>
+      <c r="B144" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C144" s="75" t="s">
         <v>153</v>
       </c>
@@ -10443,7 +10723,9 @@
       <c r="A145" s="74">
         <v>142</v>
       </c>
-      <c r="B145" s="76"/>
+      <c r="B145" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C145" s="75" t="s">
         <v>153</v>
       </c>
@@ -10488,7 +10770,9 @@
       <c r="A146" s="74">
         <v>143</v>
       </c>
-      <c r="B146" s="76"/>
+      <c r="B146" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C146" s="75" t="s">
         <v>153</v>
       </c>
@@ -10533,7 +10817,9 @@
       <c r="A147" s="74">
         <v>144</v>
       </c>
-      <c r="B147" s="76"/>
+      <c r="B147" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C147" s="75" t="s">
         <v>153</v>
       </c>
@@ -10578,7 +10864,9 @@
       <c r="A148" s="74">
         <v>145</v>
       </c>
-      <c r="B148" s="76"/>
+      <c r="B148" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C148" s="75" t="s">
         <v>177</v>
       </c>
@@ -10623,7 +10911,9 @@
       <c r="A149" s="74">
         <v>146</v>
       </c>
-      <c r="B149" s="76"/>
+      <c r="B149" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C149" s="75" t="s">
         <v>177</v>
       </c>
@@ -10668,7 +10958,9 @@
       <c r="A150" s="74">
         <v>147</v>
       </c>
-      <c r="B150" s="76"/>
+      <c r="B150" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C150" s="75" t="s">
         <v>177</v>
       </c>
@@ -10713,7 +11005,9 @@
       <c r="A151" s="74">
         <v>148</v>
       </c>
-      <c r="B151" s="76"/>
+      <c r="B151" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C151" s="75" t="s">
         <v>177</v>
       </c>
@@ -10758,7 +11052,9 @@
       <c r="A152" s="74">
         <v>149</v>
       </c>
-      <c r="B152" s="76"/>
+      <c r="B152" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C152" s="75" t="s">
         <v>177</v>
       </c>
@@ -10803,7 +11099,9 @@
       <c r="A153" s="74">
         <v>150</v>
       </c>
-      <c r="B153" s="76"/>
+      <c r="B153" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C153" s="75" t="s">
         <v>177</v>
       </c>
@@ -10862,7 +11160,9 @@
       <c r="A154" s="74">
         <v>151</v>
       </c>
-      <c r="B154" s="76"/>
+      <c r="B154" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C154" s="75" t="s">
         <v>177</v>
       </c>
@@ -10921,7 +11221,9 @@
       <c r="A155" s="74">
         <v>152</v>
       </c>
-      <c r="B155" s="76"/>
+      <c r="B155" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C155" s="75" t="s">
         <v>177</v>
       </c>
@@ -10980,7 +11282,9 @@
       <c r="A156" s="74">
         <v>153</v>
       </c>
-      <c r="B156" s="76"/>
+      <c r="B156" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C156" s="75" t="s">
         <v>177</v>
       </c>
@@ -11027,7 +11331,9 @@
       <c r="A157" s="74">
         <v>154</v>
       </c>
-      <c r="B157" s="76"/>
+      <c r="B157" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C157" s="75" t="s">
         <v>177</v>
       </c>
@@ -11072,7 +11378,9 @@
       <c r="A158" s="74">
         <v>155</v>
       </c>
-      <c r="B158" s="76"/>
+      <c r="B158" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C158" s="75" t="s">
         <v>177</v>
       </c>
@@ -11131,7 +11439,9 @@
       <c r="A159" s="74">
         <v>156</v>
       </c>
-      <c r="B159" s="76"/>
+      <c r="B159" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C159" s="75" t="s">
         <v>177</v>
       </c>
@@ -11176,7 +11486,9 @@
       <c r="A160" s="74">
         <v>157</v>
       </c>
-      <c r="B160" s="76"/>
+      <c r="B160" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C160" s="75" t="s">
         <v>177</v>
       </c>
@@ -11235,7 +11547,9 @@
       <c r="A161" s="74">
         <v>158</v>
       </c>
-      <c r="B161" s="76"/>
+      <c r="B161" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C161" s="75" t="s">
         <v>177</v>
       </c>
@@ -11280,7 +11594,9 @@
       <c r="A162" s="74">
         <v>159</v>
       </c>
-      <c r="B162" s="76"/>
+      <c r="B162" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C162" s="75" t="s">
         <v>177</v>
       </c>
@@ -11339,7 +11655,9 @@
       <c r="A163" s="74">
         <v>160</v>
       </c>
-      <c r="B163" s="76"/>
+      <c r="B163" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C163" s="75" t="s">
         <v>177</v>
       </c>
@@ -11398,7 +11716,9 @@
       <c r="A164" s="74">
         <v>161</v>
       </c>
-      <c r="B164" s="76"/>
+      <c r="B164" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C164" s="75" t="s">
         <v>177</v>
       </c>
@@ -11443,7 +11763,9 @@
       <c r="A165" s="74">
         <v>162</v>
       </c>
-      <c r="B165" s="76"/>
+      <c r="B165" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C165" s="75" t="s">
         <v>177</v>
       </c>
@@ -11502,7 +11824,9 @@
       <c r="A166" s="74">
         <v>163</v>
       </c>
-      <c r="B166" s="76"/>
+      <c r="B166" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C166" s="75" t="s">
         <v>177</v>
       </c>
@@ -11547,7 +11871,9 @@
       <c r="A167" s="74">
         <v>164</v>
       </c>
-      <c r="B167" s="76"/>
+      <c r="B167" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C167" s="75" t="s">
         <v>177</v>
       </c>
@@ -11604,7 +11930,9 @@
       <c r="A168" s="74">
         <v>165</v>
       </c>
-      <c r="B168" s="76"/>
+      <c r="B168" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C168" s="75" t="s">
         <v>177</v>
       </c>
@@ -11649,7 +11977,9 @@
       <c r="A169" s="74">
         <v>166</v>
       </c>
-      <c r="B169" s="76"/>
+      <c r="B169" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C169" s="75" t="s">
         <v>177</v>
       </c>
@@ -11694,7 +12024,9 @@
       <c r="A170" s="74">
         <v>167</v>
       </c>
-      <c r="B170" s="76"/>
+      <c r="B170" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C170" s="75" t="s">
         <v>198</v>
       </c>
@@ -11739,7 +12071,9 @@
       <c r="A171" s="74">
         <v>168</v>
       </c>
-      <c r="B171" s="76"/>
+      <c r="B171" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C171" s="75" t="s">
         <v>198</v>
       </c>
@@ -11784,7 +12118,9 @@
       <c r="A172" s="74">
         <v>169</v>
       </c>
-      <c r="B172" s="76"/>
+      <c r="B172" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C172" s="75" t="s">
         <v>198</v>
       </c>
@@ -11829,7 +12165,9 @@
       <c r="A173" s="74">
         <v>170</v>
       </c>
-      <c r="B173" s="76"/>
+      <c r="B173" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C173" s="75" t="s">
         <v>198</v>
       </c>
@@ -11874,7 +12212,9 @@
       <c r="A174" s="74">
         <v>171</v>
       </c>
-      <c r="B174" s="76"/>
+      <c r="B174" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C174" s="75" t="s">
         <v>198</v>
       </c>
@@ -11915,7 +12255,9 @@
       <c r="A175" s="74">
         <v>172</v>
       </c>
-      <c r="B175" s="76"/>
+      <c r="B175" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C175" s="75" t="s">
         <v>198</v>
       </c>
@@ -11960,7 +12302,9 @@
       <c r="A176" s="74">
         <v>173</v>
       </c>
-      <c r="B176" s="76"/>
+      <c r="B176" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C176" s="75" t="s">
         <v>204</v>
       </c>
@@ -12005,7 +12349,9 @@
       <c r="A177" s="74">
         <v>174</v>
       </c>
-      <c r="B177" s="76"/>
+      <c r="B177" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C177" s="75" t="s">
         <v>204</v>
       </c>
@@ -12060,7 +12406,9 @@
       <c r="A178" s="74">
         <v>175</v>
       </c>
-      <c r="B178" s="76"/>
+      <c r="B178" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C178" s="75" t="s">
         <v>204</v>
       </c>
@@ -12105,7 +12453,9 @@
       <c r="A179" s="74">
         <v>176</v>
       </c>
-      <c r="B179" s="76"/>
+      <c r="B179" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C179" s="75" t="s">
         <v>204</v>
       </c>
@@ -12160,7 +12510,9 @@
       <c r="A180" s="74">
         <v>177</v>
       </c>
-      <c r="B180" s="76"/>
+      <c r="B180" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C180" s="75" t="s">
         <v>204</v>
       </c>
@@ -12205,7 +12557,9 @@
       <c r="A181" s="74">
         <v>178</v>
       </c>
-      <c r="B181" s="76"/>
+      <c r="B181" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C181" s="75" t="s">
         <v>204</v>
       </c>
@@ -12250,7 +12604,9 @@
       <c r="A182" s="74">
         <v>179</v>
       </c>
-      <c r="B182" s="76"/>
+      <c r="B182" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C182" s="75" t="s">
         <v>204</v>
       </c>
@@ -12295,7 +12651,9 @@
       <c r="A183" s="74">
         <v>180</v>
       </c>
-      <c r="B183" s="76"/>
+      <c r="B183" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C183" s="75" t="s">
         <v>204</v>
       </c>
@@ -12354,7 +12712,9 @@
       <c r="A184" s="74">
         <v>181</v>
       </c>
-      <c r="B184" s="76"/>
+      <c r="B184" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C184" s="75" t="s">
         <v>204</v>
       </c>
@@ -12399,7 +12759,9 @@
       <c r="A185" s="74">
         <v>182</v>
       </c>
-      <c r="B185" s="76"/>
+      <c r="B185" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C185" s="75" t="s">
         <v>204</v>
       </c>
@@ -12458,7 +12820,9 @@
       <c r="A186" s="74">
         <v>183</v>
       </c>
-      <c r="B186" s="76"/>
+      <c r="B186" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C186" s="75" t="s">
         <v>204</v>
       </c>
@@ -12503,7 +12867,9 @@
       <c r="A187" s="74">
         <v>184</v>
       </c>
-      <c r="B187" s="76"/>
+      <c r="B187" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C187" s="75" t="s">
         <v>204</v>
       </c>
@@ -12562,7 +12928,9 @@
       <c r="A188" s="74">
         <v>185</v>
       </c>
-      <c r="B188" s="76"/>
+      <c r="B188" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C188" s="75" t="s">
         <v>204</v>
       </c>
@@ -12621,7 +12989,9 @@
       <c r="A189" s="74">
         <v>186</v>
       </c>
-      <c r="B189" s="76"/>
+      <c r="B189" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C189" s="75" t="s">
         <v>204</v>
       </c>
@@ -12666,7 +13036,9 @@
       <c r="A190" s="74">
         <v>187</v>
       </c>
-      <c r="B190" s="76"/>
+      <c r="B190" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C190" s="75" t="s">
         <v>204</v>
       </c>
@@ -12725,7 +13097,9 @@
       <c r="A191" s="74">
         <v>188</v>
       </c>
-      <c r="B191" s="76"/>
+      <c r="B191" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C191" s="75" t="s">
         <v>204</v>
       </c>
@@ -12770,7 +13144,9 @@
       <c r="A192" s="74">
         <v>189</v>
       </c>
-      <c r="B192" s="76"/>
+      <c r="B192" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C192" s="75" t="s">
         <v>204</v>
       </c>
@@ -12829,7 +13205,9 @@
       <c r="A193" s="74">
         <v>190</v>
       </c>
-      <c r="B193" s="76"/>
+      <c r="B193" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C193" s="75" t="s">
         <v>204</v>
       </c>
@@ -12874,7 +13252,9 @@
       <c r="A194" s="74">
         <v>191</v>
       </c>
-      <c r="B194" s="76"/>
+      <c r="B194" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C194" s="75" t="s">
         <v>204</v>
       </c>
@@ -12919,7 +13299,9 @@
       <c r="A195" s="74">
         <v>192</v>
       </c>
-      <c r="B195" s="76"/>
+      <c r="B195" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C195" s="75" t="s">
         <v>204</v>
       </c>
@@ -12964,7 +13346,9 @@
       <c r="A196" s="83">
         <v>193</v>
       </c>
-      <c r="B196" s="84"/>
+      <c r="B196" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C196" s="85" t="s">
         <v>224</v>
       </c>
@@ -13009,7 +13393,9 @@
       <c r="A197" s="83">
         <v>194</v>
       </c>
-      <c r="B197" s="84"/>
+      <c r="B197" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C197" s="85" t="s">
         <v>224</v>
       </c>
@@ -13054,7 +13440,9 @@
       <c r="A198" s="83">
         <v>195</v>
       </c>
-      <c r="B198" s="84"/>
+      <c r="B198" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C198" s="85" t="s">
         <v>224</v>
       </c>
@@ -13095,7 +13483,9 @@
       <c r="A199" s="83">
         <v>196</v>
       </c>
-      <c r="B199" s="84"/>
+      <c r="B199" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C199" s="85" t="s">
         <v>224</v>
       </c>
@@ -13140,7 +13530,9 @@
       <c r="A200" s="74">
         <v>197</v>
       </c>
-      <c r="B200" s="76"/>
+      <c r="B200" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C200" s="75" t="s">
         <v>229</v>
       </c>
@@ -13185,7 +13577,9 @@
       <c r="A201" s="74">
         <v>198</v>
       </c>
-      <c r="B201" s="76"/>
+      <c r="B201" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C201" s="75" t="s">
         <v>229</v>
       </c>
@@ -13230,7 +13624,9 @@
       <c r="A202" s="74">
         <v>199</v>
       </c>
-      <c r="B202" s="76"/>
+      <c r="B202" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C202" s="75" t="s">
         <v>229</v>
       </c>
@@ -13275,7 +13671,9 @@
       <c r="A203" s="74">
         <v>200</v>
       </c>
-      <c r="B203" s="76"/>
+      <c r="B203" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C203" s="75" t="s">
         <v>229</v>
       </c>
@@ -13320,7 +13718,9 @@
       <c r="A204" s="74">
         <v>201</v>
       </c>
-      <c r="B204" s="76"/>
+      <c r="B204" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C204" s="75" t="s">
         <v>229</v>
       </c>
@@ -13365,7 +13765,9 @@
       <c r="A205" s="74">
         <v>202</v>
       </c>
-      <c r="B205" s="76"/>
+      <c r="B205" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C205" s="75" t="s">
         <v>229</v>
       </c>
@@ -13406,7 +13808,9 @@
       <c r="A206" s="74">
         <v>203</v>
       </c>
-      <c r="B206" s="76"/>
+      <c r="B206" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C206" s="75" t="s">
         <v>229</v>
       </c>
@@ -13451,7 +13855,9 @@
       <c r="A207" s="74">
         <v>204</v>
       </c>
-      <c r="B207" s="76"/>
+      <c r="B207" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C207" s="75" t="s">
         <v>229</v>
       </c>
@@ -13496,7 +13902,9 @@
       <c r="A208" s="74">
         <v>205</v>
       </c>
-      <c r="B208" s="76"/>
+      <c r="B208" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C208" s="75" t="s">
         <v>229</v>
       </c>
@@ -13541,7 +13949,9 @@
       <c r="A209" s="74">
         <v>206</v>
       </c>
-      <c r="B209" s="76"/>
+      <c r="B209" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C209" s="75" t="s">
         <v>229</v>
       </c>
@@ -13588,7 +13998,9 @@
       <c r="A210" s="74">
         <v>207</v>
       </c>
-      <c r="B210" s="76"/>
+      <c r="B210" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C210" s="75" t="s">
         <v>229</v>
       </c>
@@ -13633,7 +14045,9 @@
       <c r="A211" s="83">
         <v>208</v>
       </c>
-      <c r="B211" s="84"/>
+      <c r="B211" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C211" s="85" t="s">
         <v>241</v>
       </c>
@@ -13674,7 +14088,9 @@
       <c r="A212" s="83">
         <v>209</v>
       </c>
-      <c r="B212" s="84"/>
+      <c r="B212" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C212" s="85" t="s">
         <v>241</v>
       </c>
@@ -13713,7 +14129,9 @@
       <c r="A213" s="83">
         <v>210</v>
       </c>
-      <c r="B213" s="84"/>
+      <c r="B213" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C213" s="85" t="s">
         <v>241</v>
       </c>
@@ -13758,7 +14176,9 @@
       <c r="A214" s="83">
         <v>211</v>
       </c>
-      <c r="B214" s="84"/>
+      <c r="B214" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C214" s="85" t="s">
         <v>241</v>
       </c>
@@ -13803,7 +14223,9 @@
       <c r="A215" s="83">
         <v>212</v>
       </c>
-      <c r="B215" s="84"/>
+      <c r="B215" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C215" s="85" t="s">
         <v>241</v>
       </c>
@@ -13848,7 +14270,9 @@
       <c r="A216" s="83">
         <v>213</v>
       </c>
-      <c r="B216" s="84"/>
+      <c r="B216" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C216" s="85" t="s">
         <v>241</v>
       </c>
@@ -13893,7 +14317,9 @@
       <c r="A217" s="83">
         <v>214</v>
       </c>
-      <c r="B217" s="84"/>
+      <c r="B217" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C217" s="85" t="s">
         <v>241</v>
       </c>
@@ -13938,7 +14364,9 @@
       <c r="A218" s="83">
         <v>215</v>
       </c>
-      <c r="B218" s="84"/>
+      <c r="B218" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C218" s="85" t="s">
         <v>241</v>
       </c>
@@ -13983,7 +14411,9 @@
       <c r="A219" s="83">
         <v>216</v>
       </c>
-      <c r="B219" s="84"/>
+      <c r="B219" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C219" s="85" t="s">
         <v>241</v>
       </c>
@@ -14028,7 +14458,9 @@
       <c r="A220" s="83">
         <v>217</v>
       </c>
-      <c r="B220" s="84"/>
+      <c r="B220" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C220" s="85" t="s">
         <v>241</v>
       </c>
@@ -14073,7 +14505,9 @@
       <c r="A221" s="83">
         <v>218</v>
       </c>
-      <c r="B221" s="84"/>
+      <c r="B221" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C221" s="85" t="s">
         <v>241</v>
       </c>
@@ -14118,7 +14552,9 @@
       <c r="A222" s="83">
         <v>219</v>
       </c>
-      <c r="B222" s="84"/>
+      <c r="B222" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C222" s="85" t="s">
         <v>241</v>
       </c>
@@ -14177,7 +14613,9 @@
       <c r="A223" s="83">
         <v>220</v>
       </c>
-      <c r="B223" s="84"/>
+      <c r="B223" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C223" s="85" t="s">
         <v>241</v>
       </c>
@@ -14234,7 +14672,9 @@
       <c r="A224" s="83">
         <v>221</v>
       </c>
-      <c r="B224" s="84"/>
+      <c r="B224" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C224" s="85" t="s">
         <v>241</v>
       </c>
@@ -14279,7 +14719,9 @@
       <c r="A225" s="83">
         <v>222</v>
       </c>
-      <c r="B225" s="84"/>
+      <c r="B225" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C225" s="85" t="s">
         <v>241</v>
       </c>
@@ -14338,7 +14780,9 @@
       <c r="A226" s="83">
         <v>223</v>
       </c>
-      <c r="B226" s="84"/>
+      <c r="B226" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C226" s="85" t="s">
         <v>241</v>
       </c>
@@ -14383,7 +14827,9 @@
       <c r="A227" s="83">
         <v>224</v>
       </c>
-      <c r="B227" s="84"/>
+      <c r="B227" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C227" s="85" t="s">
         <v>241</v>
       </c>
@@ -14428,7 +14874,9 @@
       <c r="A228" s="74">
         <v>225</v>
       </c>
-      <c r="B228" s="76"/>
+      <c r="B228" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C228" s="75" t="s">
         <v>258</v>
       </c>
@@ -14467,7 +14915,9 @@
       <c r="A229" s="74">
         <v>226</v>
       </c>
-      <c r="B229" s="76"/>
+      <c r="B229" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C229" s="75" t="s">
         <v>258</v>
       </c>
@@ -14520,7 +14970,9 @@
       <c r="A230" s="74">
         <v>227</v>
       </c>
-      <c r="B230" s="76"/>
+      <c r="B230" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C230" s="75" t="s">
         <v>258</v>
       </c>
@@ -14565,7 +15017,9 @@
       <c r="A231" s="74">
         <v>228</v>
       </c>
-      <c r="B231" s="76"/>
+      <c r="B231" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C231" s="75" t="s">
         <v>258</v>
       </c>
@@ -14610,7 +15064,9 @@
       <c r="A232" s="74">
         <v>229</v>
       </c>
-      <c r="B232" s="76"/>
+      <c r="B232" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C232" s="75" t="s">
         <v>258</v>
       </c>
@@ -14665,7 +15121,9 @@
       <c r="A233" s="74">
         <v>230</v>
       </c>
-      <c r="B233" s="76"/>
+      <c r="B233" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C233" s="75" t="s">
         <v>258</v>
       </c>
@@ -14724,7 +15182,9 @@
       <c r="A234" s="83">
         <v>231</v>
       </c>
-      <c r="B234" s="84"/>
+      <c r="B234" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C234" s="85" t="s">
         <v>265</v>
       </c>
@@ -14783,7 +15243,9 @@
       <c r="A235" s="83">
         <v>232</v>
       </c>
-      <c r="B235" s="84"/>
+      <c r="B235" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C235" s="85" t="s">
         <v>265</v>
       </c>
@@ -14844,7 +15306,9 @@
       <c r="A236" s="83">
         <v>233</v>
       </c>
-      <c r="B236" s="84"/>
+      <c r="B236" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C236" s="85" t="s">
         <v>265</v>
       </c>
@@ -14904,7 +15368,9 @@
       <c r="A237" s="83">
         <v>234</v>
       </c>
-      <c r="B237" s="84"/>
+      <c r="B237" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C237" s="85" t="s">
         <v>265</v>
       </c>
@@ -14964,7 +15430,9 @@
       <c r="A238" s="83">
         <v>235</v>
       </c>
-      <c r="B238" s="84"/>
+      <c r="B238" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C238" s="85" t="s">
         <v>265</v>
       </c>
@@ -15024,7 +15492,9 @@
       <c r="A239" s="83">
         <v>236</v>
       </c>
-      <c r="B239" s="84"/>
+      <c r="B239" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C239" s="85" t="s">
         <v>265</v>
       </c>
@@ -15083,7 +15553,9 @@
       <c r="A240" s="83">
         <v>237</v>
       </c>
-      <c r="B240" s="84"/>
+      <c r="B240" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C240" s="85" t="s">
         <v>265</v>
       </c>
@@ -15143,7 +15615,9 @@
       <c r="A241" s="83">
         <v>238</v>
       </c>
-      <c r="B241" s="84"/>
+      <c r="B241" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C241" s="85" t="s">
         <v>265</v>
       </c>
@@ -15203,7 +15677,9 @@
       <c r="A242" s="83">
         <v>239</v>
       </c>
-      <c r="B242" s="84"/>
+      <c r="B242" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C242" s="85" t="s">
         <v>265</v>
       </c>
@@ -15264,7 +15740,9 @@
       <c r="A243" s="83">
         <v>240</v>
       </c>
-      <c r="B243" s="84"/>
+      <c r="B243" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C243" s="85" t="s">
         <v>265</v>
       </c>
@@ -15324,7 +15802,9 @@
       <c r="A244" s="83">
         <v>241</v>
       </c>
-      <c r="B244" s="84"/>
+      <c r="B244" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C244" s="85" t="s">
         <v>265</v>
       </c>
@@ -15383,7 +15863,9 @@
       <c r="A245" s="83">
         <v>242</v>
       </c>
-      <c r="B245" s="84"/>
+      <c r="B245" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C245" s="85" t="s">
         <v>265</v>
       </c>
@@ -15443,7 +15925,9 @@
       <c r="A246" s="83">
         <v>243</v>
       </c>
-      <c r="B246" s="84"/>
+      <c r="B246" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C246" s="85" t="s">
         <v>265</v>
       </c>
@@ -15503,7 +15987,9 @@
       <c r="A247" s="83">
         <v>244</v>
       </c>
-      <c r="B247" s="84"/>
+      <c r="B247" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C247" s="85" t="s">
         <v>265</v>
       </c>
@@ -15562,7 +16048,9 @@
       <c r="A248" s="83">
         <v>245</v>
       </c>
-      <c r="B248" s="84"/>
+      <c r="B248" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C248" s="85" t="s">
         <v>265</v>
       </c>
@@ -15621,7 +16109,9 @@
       <c r="A249" s="74">
         <v>246</v>
       </c>
-      <c r="B249" s="76"/>
+      <c r="B249" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C249" s="75" t="s">
         <v>279</v>
       </c>
@@ -15666,7 +16156,9 @@
       <c r="A250" s="74">
         <v>247</v>
       </c>
-      <c r="B250" s="76"/>
+      <c r="B250" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C250" s="75" t="s">
         <v>279</v>
       </c>
@@ -15711,7 +16203,9 @@
       <c r="A251" s="74">
         <v>248</v>
       </c>
-      <c r="B251" s="76"/>
+      <c r="B251" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C251" s="75" t="s">
         <v>279</v>
       </c>
@@ -15756,7 +16250,9 @@
       <c r="A252" s="74">
         <v>249</v>
       </c>
-      <c r="B252" s="76"/>
+      <c r="B252" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C252" s="75" t="s">
         <v>279</v>
       </c>
@@ -15801,7 +16297,9 @@
       <c r="A253" s="74">
         <v>250</v>
       </c>
-      <c r="B253" s="76"/>
+      <c r="B253" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C253" s="75" t="s">
         <v>279</v>
       </c>
@@ -15846,7 +16344,9 @@
       <c r="A254" s="74">
         <v>251</v>
       </c>
-      <c r="B254" s="76"/>
+      <c r="B254" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C254" s="75" t="s">
         <v>279</v>
       </c>
@@ -15905,7 +16405,9 @@
       <c r="A255" s="74">
         <v>252</v>
       </c>
-      <c r="B255" s="76"/>
+      <c r="B255" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C255" s="75" t="s">
         <v>279</v>
       </c>
@@ -15950,7 +16452,9 @@
       <c r="A256" s="74">
         <v>253</v>
       </c>
-      <c r="B256" s="76"/>
+      <c r="B256" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C256" s="75" t="s">
         <v>279</v>
       </c>
@@ -15995,7 +16499,9 @@
       <c r="A257" s="74">
         <v>254</v>
       </c>
-      <c r="B257" s="76"/>
+      <c r="B257" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C257" s="75" t="s">
         <v>279</v>
       </c>
@@ -16040,7 +16546,9 @@
       <c r="A258" s="74">
         <v>255</v>
       </c>
-      <c r="B258" s="76"/>
+      <c r="B258" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C258" s="75" t="s">
         <v>279</v>
       </c>
@@ -16085,7 +16593,9 @@
       <c r="A259" s="74">
         <v>256</v>
       </c>
-      <c r="B259" s="76"/>
+      <c r="B259" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C259" s="75" t="s">
         <v>279</v>
       </c>
@@ -16144,7 +16654,9 @@
       <c r="A260" s="74">
         <v>257</v>
       </c>
-      <c r="B260" s="76"/>
+      <c r="B260" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C260" s="75" t="s">
         <v>289</v>
       </c>
@@ -16189,7 +16701,9 @@
       <c r="A261" s="74">
         <v>258</v>
       </c>
-      <c r="B261" s="76"/>
+      <c r="B261" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C261" s="75" t="s">
         <v>289</v>
       </c>
@@ -16248,7 +16762,9 @@
       <c r="A262" s="74">
         <v>259</v>
       </c>
-      <c r="B262" s="76"/>
+      <c r="B262" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C262" s="75" t="s">
         <v>289</v>
       </c>
@@ -16293,7 +16809,9 @@
       <c r="A263" s="74">
         <v>260</v>
       </c>
-      <c r="B263" s="76"/>
+      <c r="B263" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C263" s="75" t="s">
         <v>289</v>
       </c>
@@ -16334,7 +16852,9 @@
       <c r="A264" s="74">
         <v>261</v>
       </c>
-      <c r="B264" s="76"/>
+      <c r="B264" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C264" s="75" t="s">
         <v>289</v>
       </c>
@@ -16375,7 +16895,9 @@
       <c r="A265" s="74">
         <v>262</v>
       </c>
-      <c r="B265" s="76"/>
+      <c r="B265" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C265" s="75" t="s">
         <v>289</v>
       </c>
@@ -16420,7 +16942,9 @@
       <c r="A266" s="74">
         <v>263</v>
       </c>
-      <c r="B266" s="76"/>
+      <c r="B266" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C266" s="75" t="s">
         <v>289</v>
       </c>
@@ -16465,7 +16989,9 @@
       <c r="A267" s="74">
         <v>264</v>
       </c>
-      <c r="B267" s="76"/>
+      <c r="B267" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C267" s="75" t="s">
         <v>289</v>
       </c>
@@ -16510,7 +17036,9 @@
       <c r="A268" s="74">
         <v>265</v>
       </c>
-      <c r="B268" s="76"/>
+      <c r="B268" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C268" s="75" t="s">
         <v>289</v>
       </c>
@@ -16569,7 +17097,9 @@
       <c r="A269" s="74">
         <v>266</v>
       </c>
-      <c r="B269" s="76"/>
+      <c r="B269" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C269" s="75" t="s">
         <v>289</v>
       </c>
@@ -16628,7 +17158,9 @@
       <c r="A270" s="74">
         <v>267</v>
       </c>
-      <c r="B270" s="76"/>
+      <c r="B270" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C270" s="75" t="s">
         <v>289</v>
       </c>
@@ -16673,7 +17205,9 @@
       <c r="A271" s="74">
         <v>268</v>
       </c>
-      <c r="B271" s="76"/>
+      <c r="B271" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C271" s="75" t="s">
         <v>289</v>
       </c>
@@ -16718,7 +17252,9 @@
       <c r="A272" s="74">
         <v>269</v>
       </c>
-      <c r="B272" s="76"/>
+      <c r="B272" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C272" s="75" t="s">
         <v>289</v>
       </c>
@@ -16763,7 +17299,9 @@
       <c r="A273" s="74">
         <v>270</v>
       </c>
-      <c r="B273" s="76"/>
+      <c r="B273" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C273" s="75" t="s">
         <v>302</v>
       </c>
@@ -16820,7 +17358,9 @@
       <c r="A274" s="74">
         <v>271</v>
       </c>
-      <c r="B274" s="76"/>
+      <c r="B274" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C274" s="75" t="s">
         <v>302</v>
       </c>
@@ -16861,7 +17401,9 @@
       <c r="A275" s="74">
         <v>272</v>
       </c>
-      <c r="B275" s="76"/>
+      <c r="B275" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C275" s="75" t="s">
         <v>302</v>
       </c>
@@ -16920,7 +17462,9 @@
       <c r="A276" s="74">
         <v>273</v>
       </c>
-      <c r="B276" s="76"/>
+      <c r="B276" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C276" s="75" t="s">
         <v>302</v>
       </c>
@@ -16975,7 +17519,9 @@
       <c r="A277" s="74">
         <v>274</v>
       </c>
-      <c r="B277" s="76"/>
+      <c r="B277" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C277" s="75" t="s">
         <v>302</v>
       </c>
@@ -17034,7 +17580,9 @@
       <c r="A278" s="74">
         <v>275</v>
       </c>
-      <c r="B278" s="76"/>
+      <c r="B278" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C278" s="75" t="s">
         <v>302</v>
       </c>
@@ -17093,7 +17641,9 @@
       <c r="A279" s="74">
         <v>276</v>
       </c>
-      <c r="B279" s="76"/>
+      <c r="B279" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C279" s="75" t="s">
         <v>302</v>
       </c>
@@ -17152,7 +17702,9 @@
       <c r="A280" s="74">
         <v>277</v>
       </c>
-      <c r="B280" s="76"/>
+      <c r="B280" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C280" s="75" t="s">
         <v>310</v>
       </c>
@@ -17197,7 +17749,9 @@
       <c r="A281" s="74">
         <v>278</v>
       </c>
-      <c r="B281" s="76"/>
+      <c r="B281" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C281" s="75" t="s">
         <v>310</v>
       </c>
@@ -17238,7 +17792,9 @@
       <c r="A282" s="74">
         <v>279</v>
       </c>
-      <c r="B282" s="76"/>
+      <c r="B282" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C282" s="75" t="s">
         <v>310</v>
       </c>
@@ -17279,7 +17835,9 @@
       <c r="A283" s="74">
         <v>280</v>
       </c>
-      <c r="B283" s="76"/>
+      <c r="B283" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C283" s="75" t="s">
         <v>310</v>
       </c>
@@ -17326,7 +17884,9 @@
       <c r="A284" s="74">
         <v>281</v>
       </c>
-      <c r="B284" s="76"/>
+      <c r="B284" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C284" s="75" t="s">
         <v>310</v>
       </c>
@@ -17371,7 +17931,9 @@
       <c r="A285" s="74">
         <v>282</v>
       </c>
-      <c r="B285" s="76"/>
+      <c r="B285" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C285" s="75" t="s">
         <v>315</v>
       </c>
@@ -17410,7 +17972,9 @@
       <c r="A286" s="74">
         <v>283</v>
       </c>
-      <c r="B286" s="76"/>
+      <c r="B286" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C286" s="75" t="s">
         <v>315</v>
       </c>
@@ -17449,7 +18013,9 @@
       <c r="A287" s="74">
         <v>284</v>
       </c>
-      <c r="B287" s="76"/>
+      <c r="B287" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C287" s="75" t="s">
         <v>315</v>
       </c>
@@ -17494,7 +18060,9 @@
       <c r="A288" s="74">
         <v>285</v>
       </c>
-      <c r="B288" s="76"/>
+      <c r="B288" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C288" s="75" t="s">
         <v>315</v>
       </c>
@@ -17539,7 +18107,9 @@
       <c r="A289" s="74">
         <v>286</v>
       </c>
-      <c r="B289" s="76"/>
+      <c r="B289" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C289" s="75" t="s">
         <v>315</v>
       </c>
@@ -17580,7 +18150,9 @@
       <c r="A290" s="74">
         <v>287</v>
       </c>
-      <c r="B290" s="76"/>
+      <c r="B290" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C290" s="75" t="s">
         <v>315</v>
       </c>
@@ -17639,7 +18211,9 @@
       <c r="A291" s="74">
         <v>288</v>
       </c>
-      <c r="B291" s="76"/>
+      <c r="B291" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C291" s="75" t="s">
         <v>315</v>
       </c>
@@ -17678,7 +18252,9 @@
       <c r="A292" s="74">
         <v>289</v>
       </c>
-      <c r="B292" s="76"/>
+      <c r="B292" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C292" s="75" t="s">
         <v>315</v>
       </c>
@@ -17723,7 +18299,9 @@
       <c r="A293" s="74">
         <v>290</v>
       </c>
-      <c r="B293" s="76"/>
+      <c r="B293" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C293" s="75" t="s">
         <v>315</v>
       </c>
@@ -17768,7 +18346,9 @@
       <c r="A294" s="74">
         <v>291</v>
       </c>
-      <c r="B294" s="76"/>
+      <c r="B294" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C294" s="75" t="s">
         <v>315</v>
       </c>
@@ -17813,7 +18393,9 @@
       <c r="A295" s="74">
         <v>292</v>
       </c>
-      <c r="B295" s="76"/>
+      <c r="B295" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C295" s="75" t="s">
         <v>315</v>
       </c>
@@ -17854,7 +18436,9 @@
       <c r="A296" s="74">
         <v>293</v>
       </c>
-      <c r="B296" s="76"/>
+      <c r="B296" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C296" s="75" t="s">
         <v>315</v>
       </c>
@@ -17899,7 +18483,9 @@
       <c r="A297" s="74">
         <v>294</v>
       </c>
-      <c r="B297" s="76"/>
+      <c r="B297" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C297" s="75" t="s">
         <v>315</v>
       </c>
@@ -17944,7 +18530,9 @@
       <c r="A298" s="74">
         <v>295</v>
       </c>
-      <c r="B298" s="76"/>
+      <c r="B298" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C298" s="75" t="s">
         <v>315</v>
       </c>
@@ -17997,7 +18585,9 @@
       <c r="A299" s="74">
         <v>296</v>
       </c>
-      <c r="B299" s="76"/>
+      <c r="B299" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C299" s="75" t="s">
         <v>315</v>
       </c>
@@ -18042,7 +18632,9 @@
       <c r="A300" s="74">
         <v>297</v>
       </c>
-      <c r="B300" s="76"/>
+      <c r="B300" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C300" s="75" t="s">
         <v>315</v>
       </c>
@@ -18093,7 +18685,9 @@
       <c r="A301" s="74">
         <v>298</v>
       </c>
-      <c r="B301" s="76"/>
+      <c r="B301" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C301" s="75" t="s">
         <v>315</v>
       </c>
@@ -18144,7 +18738,9 @@
       <c r="A302" s="74">
         <v>299</v>
       </c>
-      <c r="B302" s="76"/>
+      <c r="B302" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C302" s="75" t="s">
         <v>315</v>
       </c>
@@ -18189,7 +18785,9 @@
       <c r="A303" s="74">
         <v>300</v>
       </c>
-      <c r="B303" s="76"/>
+      <c r="B303" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C303" s="75" t="s">
         <v>315</v>
       </c>
@@ -18234,7 +18832,9 @@
       <c r="A304" s="74">
         <v>301</v>
       </c>
-      <c r="B304" s="76"/>
+      <c r="B304" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C304" s="75" t="s">
         <v>315</v>
       </c>
@@ -18279,7 +18879,9 @@
       <c r="A305" s="74">
         <v>302</v>
       </c>
-      <c r="B305" s="76"/>
+      <c r="B305" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C305" s="75" t="s">
         <v>315</v>
       </c>
@@ -18324,7 +18926,9 @@
       <c r="A306" s="74">
         <v>303</v>
       </c>
-      <c r="B306" s="76"/>
+      <c r="B306" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C306" s="75" t="s">
         <v>315</v>
       </c>
@@ -18383,7 +18987,9 @@
       <c r="A307" s="74">
         <v>304</v>
       </c>
-      <c r="B307" s="76"/>
+      <c r="B307" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C307" s="75" t="s">
         <v>315</v>
       </c>
@@ -18434,7 +19040,9 @@
       <c r="A308" s="74">
         <v>305</v>
       </c>
-      <c r="B308" s="76"/>
+      <c r="B308" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C308" s="75" t="s">
         <v>315</v>
       </c>
@@ -18479,7 +19087,9 @@
       <c r="A309" s="74">
         <v>306</v>
       </c>
-      <c r="B309" s="76"/>
+      <c r="B309" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C309" s="75" t="s">
         <v>315</v>
       </c>
@@ -18538,7 +19148,9 @@
       <c r="A310" s="74">
         <v>307</v>
       </c>
-      <c r="B310" s="76"/>
+      <c r="B310" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C310" s="75" t="s">
         <v>315</v>
       </c>
@@ -18583,7 +19195,9 @@
       <c r="A311" s="74">
         <v>308</v>
       </c>
-      <c r="B311" s="76"/>
+      <c r="B311" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C311" s="75" t="s">
         <v>315</v>
       </c>
@@ -18642,7 +19256,9 @@
       <c r="A312" s="74">
         <v>309</v>
       </c>
-      <c r="B312" s="76"/>
+      <c r="B312" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C312" s="75" t="s">
         <v>315</v>
       </c>
@@ -18687,7 +19303,9 @@
       <c r="A313" s="74">
         <v>310</v>
       </c>
-      <c r="B313" s="76"/>
+      <c r="B313" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C313" s="75" t="s">
         <v>315</v>
       </c>
@@ -18746,7 +19364,9 @@
       <c r="A314" s="74">
         <v>311</v>
       </c>
-      <c r="B314" s="76"/>
+      <c r="B314" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C314" s="75" t="s">
         <v>315</v>
       </c>
@@ -18791,7 +19411,9 @@
       <c r="A315" s="74">
         <v>312</v>
       </c>
-      <c r="B315" s="76"/>
+      <c r="B315" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C315" s="75" t="s">
         <v>315</v>
       </c>
@@ -18830,7 +19452,9 @@
       <c r="A316" s="74">
         <v>313</v>
       </c>
-      <c r="B316" s="76"/>
+      <c r="B316" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C316" s="75" t="s">
         <v>315</v>
       </c>
@@ -18871,7 +19495,9 @@
       <c r="A317" s="74">
         <v>314</v>
       </c>
-      <c r="B317" s="76"/>
+      <c r="B317" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C317" s="75" t="s">
         <v>315</v>
       </c>
@@ -18912,7 +19538,9 @@
       <c r="A318" s="74">
         <v>315</v>
       </c>
-      <c r="B318" s="76"/>
+      <c r="B318" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C318" s="75" t="s">
         <v>315</v>
       </c>
@@ -18951,7 +19579,9 @@
       <c r="A319" s="74">
         <v>316</v>
       </c>
-      <c r="B319" s="76"/>
+      <c r="B319" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C319" s="75" t="s">
         <v>315</v>
       </c>
@@ -18990,7 +19620,9 @@
       <c r="A320" s="74">
         <v>317</v>
       </c>
-      <c r="B320" s="76"/>
+      <c r="B320" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C320" s="75" t="s">
         <v>315</v>
       </c>
@@ -19029,7 +19661,9 @@
       <c r="A321" s="74">
         <v>318</v>
       </c>
-      <c r="B321" s="76"/>
+      <c r="B321" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C321" s="75" t="s">
         <v>315</v>
       </c>
@@ -19088,7 +19722,9 @@
       <c r="A322" s="74">
         <v>319</v>
       </c>
-      <c r="B322" s="76"/>
+      <c r="B322" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C322" s="75" t="s">
         <v>315</v>
       </c>
@@ -19129,7 +19765,9 @@
       <c r="A323" s="74">
         <v>320</v>
       </c>
-      <c r="B323" s="76"/>
+      <c r="B323" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C323" s="75" t="s">
         <v>315</v>
       </c>
@@ -19174,7 +19812,9 @@
       <c r="A324" s="74">
         <v>321</v>
       </c>
-      <c r="B324" s="76"/>
+      <c r="B324" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C324" s="75" t="s">
         <v>315</v>
       </c>
@@ -19233,7 +19873,9 @@
       <c r="A325" s="74">
         <v>322</v>
       </c>
-      <c r="B325" s="76"/>
+      <c r="B325" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C325" s="75" t="s">
         <v>315</v>
       </c>
@@ -19278,7 +19920,9 @@
       <c r="A326" s="74">
         <v>323</v>
       </c>
-      <c r="B326" s="76"/>
+      <c r="B326" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C326" s="75" t="s">
         <v>315</v>
       </c>
@@ -19323,7 +19967,9 @@
       <c r="A327" s="74">
         <v>324</v>
       </c>
-      <c r="B327" s="76"/>
+      <c r="B327" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C327" s="75" t="s">
         <v>315</v>
       </c>
@@ -19362,7 +20008,9 @@
       <c r="A328" s="74">
         <v>325</v>
       </c>
-      <c r="B328" s="76"/>
+      <c r="B328" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C328" s="75" t="s">
         <v>315</v>
       </c>
@@ -19407,7 +20055,9 @@
       <c r="A329" s="74">
         <v>326</v>
       </c>
-      <c r="B329" s="76"/>
+      <c r="B329" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C329" s="75" t="s">
         <v>315</v>
       </c>
@@ -19452,7 +20102,9 @@
       <c r="A330" s="74">
         <v>327</v>
       </c>
-      <c r="B330" s="76"/>
+      <c r="B330" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C330" s="75" t="s">
         <v>315</v>
       </c>
@@ -19497,7 +20149,9 @@
       <c r="A331" s="74">
         <v>328</v>
       </c>
-      <c r="B331" s="76"/>
+      <c r="B331" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C331" s="75" t="s">
         <v>359</v>
       </c>
@@ -19556,7 +20210,9 @@
       <c r="A332" s="74">
         <v>329</v>
       </c>
-      <c r="B332" s="76"/>
+      <c r="B332" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C332" s="75" t="s">
         <v>359</v>
       </c>
@@ -19601,7 +20257,9 @@
       <c r="A333" s="74">
         <v>330</v>
       </c>
-      <c r="B333" s="76"/>
+      <c r="B333" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C333" s="75" t="s">
         <v>359</v>
       </c>
@@ -19646,7 +20304,9 @@
       <c r="A334" s="74">
         <v>331</v>
       </c>
-      <c r="B334" s="76"/>
+      <c r="B334" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C334" s="75" t="s">
         <v>359</v>
       </c>
@@ -19701,11 +20361,13 @@
       <c r="AB334" s="72"/>
       <c r="AC334" s="72"/>
     </row>
-    <row r="335" spans="1:29" s="73" customFormat="1" ht="41.25">
+    <row r="335" spans="1:29" s="73" customFormat="1" ht="20.65">
       <c r="A335" s="74">
         <v>332</v>
       </c>
-      <c r="B335" s="76"/>
+      <c r="B335" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C335" s="75" t="s">
         <v>364</v>
       </c>
@@ -19744,7 +20406,9 @@
       <c r="A336" s="74">
         <v>333</v>
       </c>
-      <c r="B336" s="76"/>
+      <c r="B336" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C336" s="75" t="s">
         <v>364</v>
       </c>
@@ -19783,7 +20447,9 @@
       <c r="A337" s="74">
         <v>334</v>
       </c>
-      <c r="B337" s="76"/>
+      <c r="B337" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C337" s="75" t="s">
         <v>364</v>
       </c>
@@ -19828,7 +20494,9 @@
       <c r="A338" s="74">
         <v>335</v>
       </c>
-      <c r="B338" s="76"/>
+      <c r="B338" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C338" s="75" t="s">
         <v>364</v>
       </c>
@@ -19869,7 +20537,9 @@
       <c r="A339" s="74">
         <v>336</v>
       </c>
-      <c r="B339" s="76"/>
+      <c r="B339" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C339" s="75" t="s">
         <v>364</v>
       </c>
@@ -19914,7 +20584,9 @@
       <c r="A340" s="74">
         <v>337</v>
       </c>
-      <c r="B340" s="76"/>
+      <c r="B340" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C340" s="75" t="s">
         <v>364</v>
       </c>
@@ -19955,7 +20627,9 @@
       <c r="A341" s="74">
         <v>338</v>
       </c>
-      <c r="B341" s="76"/>
+      <c r="B341" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C341" s="75" t="s">
         <v>364</v>
       </c>
@@ -20000,7 +20674,9 @@
       <c r="A342" s="74">
         <v>339</v>
       </c>
-      <c r="B342" s="76"/>
+      <c r="B342" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C342" s="75" t="s">
         <v>364</v>
       </c>
@@ -20045,7 +20721,9 @@
       <c r="A343" s="74">
         <v>340</v>
       </c>
-      <c r="B343" s="76"/>
+      <c r="B343" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C343" s="75" t="s">
         <v>364</v>
       </c>
@@ -20090,7 +20768,9 @@
       <c r="A344" s="74">
         <v>341</v>
       </c>
-      <c r="B344" s="76"/>
+      <c r="B344" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C344" s="75" t="s">
         <v>364</v>
       </c>
@@ -20135,7 +20815,9 @@
       <c r="A345" s="74">
         <v>342</v>
       </c>
-      <c r="B345" s="76"/>
+      <c r="B345" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C345" s="75" t="s">
         <v>364</v>
       </c>
@@ -20180,7 +20862,9 @@
       <c r="A346" s="74">
         <v>343</v>
       </c>
-      <c r="B346" s="76"/>
+      <c r="B346" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C346" s="75" t="s">
         <v>364</v>
       </c>
@@ -20219,7 +20903,9 @@
       <c r="A347" s="74">
         <v>344</v>
       </c>
-      <c r="B347" s="76"/>
+      <c r="B347" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C347" s="75" t="s">
         <v>377</v>
       </c>
@@ -20264,7 +20950,9 @@
       <c r="A348" s="74">
         <v>345</v>
       </c>
-      <c r="B348" s="76"/>
+      <c r="B348" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C348" s="75" t="s">
         <v>377</v>
       </c>
@@ -20309,7 +20997,9 @@
       <c r="A349" s="74">
         <v>346</v>
       </c>
-      <c r="B349" s="76"/>
+      <c r="B349" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C349" s="75" t="s">
         <v>377</v>
       </c>
@@ -20354,7 +21044,9 @@
       <c r="A350" s="74">
         <v>347</v>
       </c>
-      <c r="B350" s="76"/>
+      <c r="B350" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C350" s="75" t="s">
         <v>377</v>
       </c>
@@ -20399,7 +21091,9 @@
       <c r="A351" s="74">
         <v>348</v>
       </c>
-      <c r="B351" s="76"/>
+      <c r="B351" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C351" s="75" t="s">
         <v>377</v>
       </c>
@@ -20444,7 +21138,9 @@
       <c r="A352" s="74">
         <v>349</v>
       </c>
-      <c r="B352" s="76"/>
+      <c r="B352" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C352" s="75" t="s">
         <v>381</v>
       </c>
@@ -20489,7 +21185,9 @@
       <c r="A353" s="74">
         <v>350</v>
       </c>
-      <c r="B353" s="76"/>
+      <c r="B353" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C353" s="75" t="s">
         <v>381</v>
       </c>
@@ -20534,7 +21232,9 @@
       <c r="A354" s="74">
         <v>351</v>
       </c>
-      <c r="B354" s="76"/>
+      <c r="B354" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C354" s="75" t="s">
         <v>381</v>
       </c>
@@ -20579,7 +21279,9 @@
       <c r="A355" s="74">
         <v>352</v>
       </c>
-      <c r="B355" s="76"/>
+      <c r="B355" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C355" s="75" t="s">
         <v>381</v>
       </c>
@@ -20624,7 +21326,9 @@
       <c r="A356" s="74">
         <v>353</v>
       </c>
-      <c r="B356" s="76"/>
+      <c r="B356" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C356" s="75" t="s">
         <v>381</v>
       </c>
@@ -20669,7 +21373,9 @@
       <c r="A357" s="74">
         <v>354</v>
       </c>
-      <c r="B357" s="76"/>
+      <c r="B357" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C357" s="75" t="s">
         <v>381</v>
       </c>
@@ -20714,7 +21420,9 @@
       <c r="A358" s="74">
         <v>355</v>
       </c>
-      <c r="B358" s="76"/>
+      <c r="B358" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C358" s="75" t="s">
         <v>381</v>
       </c>
@@ -20759,7 +21467,9 @@
       <c r="A359" s="74">
         <v>356</v>
       </c>
-      <c r="B359" s="76"/>
+      <c r="B359" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C359" s="75" t="s">
         <v>381</v>
       </c>
@@ -20804,7 +21514,9 @@
       <c r="A360" s="74">
         <v>357</v>
       </c>
-      <c r="B360" s="76"/>
+      <c r="B360" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C360" s="75" t="s">
         <v>381</v>
       </c>
@@ -20863,7 +21575,9 @@
       <c r="A361" s="74">
         <v>358</v>
       </c>
-      <c r="B361" s="76"/>
+      <c r="B361" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C361" s="75" t="s">
         <v>381</v>
       </c>
@@ -20908,7 +21622,9 @@
       <c r="A362" s="74">
         <v>359</v>
       </c>
-      <c r="B362" s="76"/>
+      <c r="B362" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C362" s="75" t="s">
         <v>381</v>
       </c>
@@ -20953,7 +21669,9 @@
       <c r="A363" s="74">
         <v>360</v>
       </c>
-      <c r="B363" s="76"/>
+      <c r="B363" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C363" s="75" t="s">
         <v>381</v>
       </c>
@@ -21012,7 +21730,9 @@
       <c r="A364" s="74">
         <v>361</v>
       </c>
-      <c r="B364" s="76"/>
+      <c r="B364" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C364" s="75" t="s">
         <v>394</v>
       </c>
@@ -21071,7 +21791,9 @@
       <c r="A365" s="74">
         <v>362</v>
       </c>
-      <c r="B365" s="76"/>
+      <c r="B365" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C365" s="75" t="s">
         <v>394</v>
       </c>
@@ -21130,7 +21852,9 @@
       <c r="A366" s="74">
         <v>363</v>
       </c>
-      <c r="B366" s="76"/>
+      <c r="B366" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C366" s="75" t="s">
         <v>394</v>
       </c>
@@ -21175,7 +21899,9 @@
       <c r="A367" s="74">
         <v>364</v>
       </c>
-      <c r="B367" s="76"/>
+      <c r="B367" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C367" s="75" t="s">
         <v>394</v>
       </c>
@@ -21220,7 +21946,9 @@
       <c r="A368" s="74">
         <v>365</v>
       </c>
-      <c r="B368" s="76"/>
+      <c r="B368" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C368" s="75" t="s">
         <v>394</v>
       </c>
@@ -21265,7 +21993,9 @@
       <c r="A369" s="74">
         <v>366</v>
       </c>
-      <c r="B369" s="76"/>
+      <c r="B369" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C369" s="75" t="s">
         <v>394</v>
       </c>
@@ -21310,7 +22040,9 @@
       <c r="A370" s="74">
         <v>367</v>
       </c>
-      <c r="B370" s="76"/>
+      <c r="B370" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C370" s="75" t="s">
         <v>394</v>
       </c>
@@ -21355,7 +22087,9 @@
       <c r="A371" s="74">
         <v>368</v>
       </c>
-      <c r="B371" s="76"/>
+      <c r="B371" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C371" s="75" t="s">
         <v>394</v>
       </c>
@@ -21400,7 +22134,9 @@
       <c r="A372" s="74">
         <v>369</v>
       </c>
-      <c r="B372" s="76"/>
+      <c r="B372" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C372" s="75" t="s">
         <v>394</v>
       </c>
@@ -21445,7 +22181,9 @@
       <c r="A373" s="74">
         <v>370</v>
       </c>
-      <c r="B373" s="76"/>
+      <c r="B373" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C373" s="75" t="s">
         <v>394</v>
       </c>
@@ -21490,7 +22228,9 @@
       <c r="A374" s="74">
         <v>371</v>
       </c>
-      <c r="B374" s="76"/>
+      <c r="B374" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C374" s="75" t="s">
         <v>394</v>
       </c>
@@ -21535,7 +22275,9 @@
       <c r="A375" s="74">
         <v>372</v>
       </c>
-      <c r="B375" s="76"/>
+      <c r="B375" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C375" s="75" t="s">
         <v>394</v>
       </c>
@@ -21580,7 +22322,9 @@
       <c r="A376" s="74">
         <v>373</v>
       </c>
-      <c r="B376" s="76"/>
+      <c r="B376" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C376" s="75" t="s">
         <v>394</v>
       </c>
@@ -21625,7 +22369,9 @@
       <c r="A377" s="74">
         <v>374</v>
       </c>
-      <c r="B377" s="76"/>
+      <c r="B377" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C377" s="75" t="s">
         <v>394</v>
       </c>
@@ -21670,7 +22416,9 @@
       <c r="A378" s="74">
         <v>375</v>
       </c>
-      <c r="B378" s="76"/>
+      <c r="B378" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C378" s="75" t="s">
         <v>394</v>
       </c>
@@ -21715,7 +22463,9 @@
       <c r="A379" s="74">
         <v>376</v>
       </c>
-      <c r="B379" s="76"/>
+      <c r="B379" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C379" s="75" t="s">
         <v>394</v>
       </c>
@@ -21760,7 +22510,9 @@
       <c r="A380" s="74">
         <v>377</v>
       </c>
-      <c r="B380" s="76"/>
+      <c r="B380" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C380" s="75" t="s">
         <v>394</v>
       </c>
@@ -21801,7 +22553,9 @@
       <c r="A381" s="74">
         <v>378</v>
       </c>
-      <c r="B381" s="76"/>
+      <c r="B381" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C381" s="75" t="s">
         <v>394</v>
       </c>
@@ -21846,7 +22600,9 @@
       <c r="A382" s="74">
         <v>379</v>
       </c>
-      <c r="B382" s="76"/>
+      <c r="B382" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C382" s="75" t="s">
         <v>410</v>
       </c>
@@ -21901,7 +22657,9 @@
       <c r="A383" s="74">
         <v>380</v>
       </c>
-      <c r="B383" s="76"/>
+      <c r="B383" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C383" s="75" t="s">
         <v>410</v>
       </c>
@@ -21946,7 +22704,9 @@
       <c r="A384" s="74">
         <v>381</v>
       </c>
-      <c r="B384" s="76"/>
+      <c r="B384" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C384" s="75" t="s">
         <v>410</v>
       </c>
@@ -21991,7 +22751,9 @@
       <c r="A385" s="74">
         <v>382</v>
       </c>
-      <c r="B385" s="76"/>
+      <c r="B385" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C385" s="75" t="s">
         <v>410</v>
       </c>
@@ -22044,7 +22806,9 @@
       <c r="A386" s="74">
         <v>383</v>
       </c>
-      <c r="B386" s="76"/>
+      <c r="B386" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C386" s="75" t="s">
         <v>415</v>
       </c>
@@ -22095,7 +22859,9 @@
       <c r="A387" s="74">
         <v>384</v>
       </c>
-      <c r="B387" s="76"/>
+      <c r="B387" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C387" s="75" t="s">
         <v>415</v>
       </c>
@@ -22140,7 +22906,9 @@
       <c r="A388" s="74">
         <v>385</v>
       </c>
-      <c r="B388" s="76"/>
+      <c r="B388" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C388" s="75" t="s">
         <v>415</v>
       </c>
@@ -22185,7 +22953,9 @@
       <c r="A389" s="74">
         <v>386</v>
       </c>
-      <c r="B389" s="76"/>
+      <c r="B389" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C389" s="75" t="s">
         <v>415</v>
       </c>
@@ -22230,7 +23000,9 @@
       <c r="A390" s="74">
         <v>387</v>
       </c>
-      <c r="B390" s="76"/>
+      <c r="B390" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C390" s="75" t="s">
         <v>415</v>
       </c>
@@ -22275,7 +23047,9 @@
       <c r="A391" s="74">
         <v>388</v>
       </c>
-      <c r="B391" s="76"/>
+      <c r="B391" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C391" s="75" t="s">
         <v>415</v>
       </c>
@@ -22320,7 +23094,9 @@
       <c r="A392" s="74">
         <v>389</v>
       </c>
-      <c r="B392" s="76"/>
+      <c r="B392" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C392" s="75" t="s">
         <v>415</v>
       </c>
@@ -22365,7 +23141,9 @@
       <c r="A393" s="74">
         <v>390</v>
       </c>
-      <c r="B393" s="76"/>
+      <c r="B393" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C393" s="75" t="s">
         <v>415</v>
       </c>
@@ -22410,7 +23188,9 @@
       <c r="A394" s="74">
         <v>391</v>
       </c>
-      <c r="B394" s="76"/>
+      <c r="B394" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C394" s="75" t="s">
         <v>415</v>
       </c>
@@ -22455,7 +23235,9 @@
       <c r="A395" s="74">
         <v>392</v>
       </c>
-      <c r="B395" s="76"/>
+      <c r="B395" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C395" s="75" t="s">
         <v>415</v>
       </c>
@@ -22500,7 +23282,9 @@
       <c r="A396" s="74">
         <v>393</v>
       </c>
-      <c r="B396" s="76"/>
+      <c r="B396" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C396" s="75" t="s">
         <v>415</v>
       </c>
@@ -22545,7 +23329,9 @@
       <c r="A397" s="74">
         <v>394</v>
       </c>
-      <c r="B397" s="76"/>
+      <c r="B397" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C397" s="75" t="s">
         <v>415</v>
       </c>
@@ -22590,7 +23376,7 @@
       <c r="A398" s="86">
         <v>1</v>
       </c>
-      <c r="B398" s="86" t="s">
+      <c r="B398" s="75" t="s">
         <v>21</v>
       </c>
       <c r="C398" s="87" t="s">
@@ -22637,7 +23423,9 @@
       <c r="A399" s="86">
         <v>2</v>
       </c>
-      <c r="B399" s="88"/>
+      <c r="B399" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C399" s="87" t="s">
         <v>31</v>
       </c>
@@ -22682,7 +23470,9 @@
       <c r="A400" s="86">
         <v>3</v>
       </c>
-      <c r="B400" s="88"/>
+      <c r="B400" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C400" s="87" t="s">
         <v>39</v>
       </c>
@@ -22727,7 +23517,9 @@
       <c r="A401" s="86">
         <v>4</v>
       </c>
-      <c r="B401" s="88"/>
+      <c r="B401" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C401" s="87" t="s">
         <v>51</v>
       </c>
@@ -22772,7 +23564,9 @@
       <c r="A402" s="86">
         <v>5</v>
       </c>
-      <c r="B402" s="88"/>
+      <c r="B402" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C402" s="87" t="s">
         <v>71</v>
       </c>
@@ -22817,7 +23611,9 @@
       <c r="A403" s="86">
         <v>6</v>
       </c>
-      <c r="B403" s="88"/>
+      <c r="B403" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C403" s="87" t="s">
         <v>80</v>
       </c>
@@ -22862,7 +23658,9 @@
       <c r="A404" s="86">
         <v>7</v>
       </c>
-      <c r="B404" s="88"/>
+      <c r="B404" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C404" s="87" t="s">
         <v>94</v>
       </c>
@@ -22907,7 +23705,9 @@
       <c r="A405" s="86">
         <v>8</v>
       </c>
-      <c r="B405" s="88"/>
+      <c r="B405" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C405" s="87" t="s">
         <v>115</v>
       </c>
@@ -22966,7 +23766,9 @@
       <c r="A406" s="86">
         <v>9</v>
       </c>
-      <c r="B406" s="88"/>
+      <c r="B406" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C406" s="87" t="s">
         <v>121</v>
       </c>
@@ -23011,7 +23813,9 @@
       <c r="A407" s="86">
         <v>10</v>
       </c>
-      <c r="B407" s="88"/>
+      <c r="B407" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C407" s="87" t="s">
         <v>135</v>
       </c>
@@ -23056,7 +23860,9 @@
       <c r="A408" s="86">
         <v>11</v>
       </c>
-      <c r="B408" s="88"/>
+      <c r="B408" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C408" s="87" t="s">
         <v>140</v>
       </c>
@@ -23101,7 +23907,9 @@
       <c r="A409" s="86">
         <v>12</v>
       </c>
-      <c r="B409" s="88"/>
+      <c r="B409" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C409" s="87" t="s">
         <v>153</v>
       </c>
@@ -23146,7 +23954,9 @@
       <c r="A410" s="86">
         <v>13</v>
       </c>
-      <c r="B410" s="88"/>
+      <c r="B410" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C410" s="87" t="s">
         <v>177</v>
       </c>
@@ -23191,7 +24001,9 @@
       <c r="A411" s="86">
         <v>14</v>
       </c>
-      <c r="B411" s="88"/>
+      <c r="B411" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C411" s="87" t="s">
         <v>198</v>
       </c>
@@ -23236,7 +24048,9 @@
       <c r="A412" s="86">
         <v>15</v>
       </c>
-      <c r="B412" s="88"/>
+      <c r="B412" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C412" s="87" t="s">
         <v>204</v>
       </c>
@@ -23281,7 +24095,9 @@
       <c r="A413" s="86">
         <v>16</v>
       </c>
-      <c r="B413" s="88"/>
+      <c r="B413" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C413" s="87" t="s">
         <v>224</v>
       </c>
@@ -23326,7 +24142,9 @@
       <c r="A414" s="86">
         <v>17</v>
       </c>
-      <c r="B414" s="88"/>
+      <c r="B414" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C414" s="87" t="s">
         <v>229</v>
       </c>
@@ -23385,7 +24203,9 @@
       <c r="A415" s="86">
         <v>18</v>
       </c>
-      <c r="B415" s="88"/>
+      <c r="B415" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C415" s="87" t="s">
         <v>241</v>
       </c>
@@ -23430,7 +24250,9 @@
       <c r="A416" s="86">
         <v>19</v>
       </c>
-      <c r="B416" s="88"/>
+      <c r="B416" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C416" s="87" t="s">
         <v>258</v>
       </c>
@@ -23489,7 +24311,9 @@
       <c r="A417" s="86">
         <v>20</v>
       </c>
-      <c r="B417" s="88"/>
+      <c r="B417" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C417" s="87" t="s">
         <v>265</v>
       </c>
@@ -23534,7 +24358,9 @@
       <c r="A418" s="86">
         <v>21</v>
       </c>
-      <c r="B418" s="88"/>
+      <c r="B418" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C418" s="87" t="s">
         <v>279</v>
       </c>
@@ -23579,7 +24405,9 @@
       <c r="A419" s="86">
         <v>22</v>
       </c>
-      <c r="B419" s="88"/>
+      <c r="B419" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C419" s="87" t="s">
         <v>289</v>
       </c>
@@ -23624,7 +24452,9 @@
       <c r="A420" s="86">
         <v>23</v>
       </c>
-      <c r="B420" s="88"/>
+      <c r="B420" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C420" s="87" t="s">
         <v>302</v>
       </c>
@@ -23669,7 +24499,9 @@
       <c r="A421" s="86">
         <v>23</v>
       </c>
-      <c r="B421" s="88"/>
+      <c r="B421" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C421" s="87" t="s">
         <v>310</v>
       </c>
@@ -23710,7 +24542,9 @@
       <c r="A422" s="86">
         <v>23</v>
       </c>
-      <c r="B422" s="88"/>
+      <c r="B422" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C422" s="87" t="s">
         <v>359</v>
       </c>
@@ -23755,7 +24589,9 @@
       <c r="A423" s="86">
         <v>23</v>
       </c>
-      <c r="B423" s="88"/>
+      <c r="B423" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C423" s="87" t="s">
         <v>364</v>
       </c>
@@ -23800,7 +24636,9 @@
       <c r="A424" s="86">
         <v>23</v>
       </c>
-      <c r="B424" s="88"/>
+      <c r="B424" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C424" s="87" t="s">
         <v>377</v>
       </c>
@@ -23859,7 +24697,9 @@
       <c r="A425" s="86">
         <v>23</v>
       </c>
-      <c r="B425" s="88"/>
+      <c r="B425" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C425" s="87" t="s">
         <v>381</v>
       </c>
@@ -23904,7 +24744,9 @@
       <c r="A426" s="86">
         <v>23</v>
       </c>
-      <c r="B426" s="88"/>
+      <c r="B426" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C426" s="87" t="s">
         <v>394</v>
       </c>
@@ -23949,7 +24791,9 @@
       <c r="A427" s="86">
         <v>23</v>
       </c>
-      <c r="B427" s="88"/>
+      <c r="B427" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C427" s="87" t="s">
         <v>410</v>
       </c>
@@ -23994,7 +24838,9 @@
       <c r="A428" s="86">
         <v>23</v>
       </c>
-      <c r="B428" s="88"/>
+      <c r="B428" s="75" t="s">
+        <v>21</v>
+      </c>
       <c r="C428" s="87" t="s">
         <v>415</v>
       </c>
@@ -41283,20 +42129,20 @@
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="F1:H2"/>
+    <mergeCell ref="O2:O3"/>
+    <mergeCell ref="I1:O1"/>
+    <mergeCell ref="A1:A3"/>
+    <mergeCell ref="B1:B3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:E3"/>
     <mergeCell ref="P1:R1"/>
     <mergeCell ref="I2:I3"/>
     <mergeCell ref="J2:K2"/>
     <mergeCell ref="L2:M2"/>
     <mergeCell ref="N2:N3"/>
     <mergeCell ref="P2:R2"/>
-    <mergeCell ref="A1:A3"/>
-    <mergeCell ref="B1:B3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:E3"/>
-    <mergeCell ref="F1:H2"/>
-    <mergeCell ref="O2:O3"/>
-    <mergeCell ref="I1:O1"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -41371,40 +42217,40 @@
       <c r="X1" s="15"/>
     </row>
     <row r="2" spans="1:24" ht="20.65">
-      <c r="A2" s="111" t="s">
+      <c r="A2" s="112" t="s">
         <v>458</v>
       </c>
-      <c r="B2" s="111" t="s">
+      <c r="B2" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="111" t="s">
+      <c r="C2" s="112" t="s">
         <v>459</v>
       </c>
-      <c r="D2" s="111" t="s">
+      <c r="D2" s="112" t="s">
         <v>460</v>
       </c>
-      <c r="E2" s="111" t="s">
+      <c r="E2" s="112" t="s">
         <v>461</v>
       </c>
-      <c r="F2" s="114" t="s">
+      <c r="F2" s="115" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="94"/>
-      <c r="H2" s="95"/>
-      <c r="I2" s="119" t="s">
+      <c r="G2" s="103"/>
+      <c r="H2" s="104"/>
+      <c r="I2" s="113" t="s">
         <v>462</v>
       </c>
-      <c r="J2" s="102"/>
-      <c r="K2" s="102"/>
-      <c r="L2" s="102"/>
-      <c r="M2" s="102"/>
-      <c r="N2" s="102"/>
-      <c r="O2" s="103"/>
-      <c r="P2" s="113" t="s">
+      <c r="J2" s="91"/>
+      <c r="K2" s="91"/>
+      <c r="L2" s="91"/>
+      <c r="M2" s="91"/>
+      <c r="N2" s="91"/>
+      <c r="O2" s="92"/>
+      <c r="P2" s="114" t="s">
         <v>7</v>
       </c>
-      <c r="Q2" s="102"/>
-      <c r="R2" s="103"/>
+      <c r="Q2" s="91"/>
+      <c r="R2" s="92"/>
       <c r="S2" s="16"/>
       <c r="T2" s="16"/>
       <c r="U2" s="16"/>
@@ -41413,36 +42259,36 @@
       <c r="X2" s="16"/>
     </row>
     <row r="3" spans="1:24" ht="20.65">
-      <c r="A3" s="91"/>
-      <c r="B3" s="91"/>
-      <c r="C3" s="91"/>
-      <c r="D3" s="91"/>
-      <c r="E3" s="91"/>
-      <c r="F3" s="96"/>
-      <c r="G3" s="97"/>
-      <c r="H3" s="98"/>
-      <c r="I3" s="118" t="s">
+      <c r="A3" s="98"/>
+      <c r="B3" s="98"/>
+      <c r="C3" s="98"/>
+      <c r="D3" s="98"/>
+      <c r="E3" s="98"/>
+      <c r="F3" s="105"/>
+      <c r="G3" s="106"/>
+      <c r="H3" s="107"/>
+      <c r="I3" s="120" t="s">
         <v>463</v>
       </c>
-      <c r="J3" s="115" t="s">
+      <c r="J3" s="116" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="103"/>
-      <c r="L3" s="119" t="s">
+      <c r="K3" s="92"/>
+      <c r="L3" s="113" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="102"/>
-      <c r="N3" s="120" t="s">
+      <c r="M3" s="91"/>
+      <c r="N3" s="121" t="s">
         <v>464</v>
       </c>
-      <c r="O3" s="121" t="s">
+      <c r="O3" s="111" t="s">
         <v>12</v>
       </c>
-      <c r="P3" s="113" t="s">
+      <c r="P3" s="114" t="s">
         <v>465</v>
       </c>
-      <c r="Q3" s="102"/>
-      <c r="R3" s="103"/>
+      <c r="Q3" s="91"/>
+      <c r="R3" s="92"/>
       <c r="S3" s="16"/>
       <c r="T3" s="16"/>
       <c r="U3" s="16"/>
@@ -41451,11 +42297,11 @@
       <c r="X3" s="16"/>
     </row>
     <row r="4" spans="1:24" ht="64.5" customHeight="1">
-      <c r="A4" s="91"/>
-      <c r="B4" s="91"/>
-      <c r="C4" s="91"/>
-      <c r="D4" s="91"/>
-      <c r="E4" s="91"/>
+      <c r="A4" s="98"/>
+      <c r="B4" s="98"/>
+      <c r="C4" s="98"/>
+      <c r="D4" s="98"/>
+      <c r="E4" s="98"/>
       <c r="F4" s="19" t="s">
         <v>14</v>
       </c>
@@ -41465,7 +42311,7 @@
       <c r="H4" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="I4" s="106"/>
+      <c r="I4" s="94"/>
       <c r="J4" s="17" t="s">
         <v>15</v>
       </c>
@@ -41478,8 +42324,8 @@
       <c r="M4" s="22" t="s">
         <v>18</v>
       </c>
-      <c r="N4" s="91"/>
-      <c r="O4" s="100"/>
+      <c r="N4" s="98"/>
+      <c r="O4" s="109"/>
       <c r="P4" s="23" t="s">
         <v>466</v>
       </c>
@@ -51623,40 +52469,40 @@
       <c r="X232" s="50"/>
     </row>
     <row r="233" spans="1:24" ht="20.65">
-      <c r="A233" s="111" t="s">
+      <c r="A233" s="112" t="s">
         <v>458</v>
       </c>
-      <c r="B233" s="111" t="s">
+      <c r="B233" s="112" t="s">
         <v>1</v>
       </c>
-      <c r="C233" s="111" t="s">
+      <c r="C233" s="112" t="s">
         <v>459</v>
       </c>
-      <c r="D233" s="111" t="s">
+      <c r="D233" s="112" t="s">
         <v>460</v>
       </c>
-      <c r="E233" s="111" t="s">
+      <c r="E233" s="112" t="s">
         <v>461</v>
       </c>
-      <c r="F233" s="114" t="s">
+      <c r="F233" s="115" t="s">
         <v>5</v>
       </c>
-      <c r="G233" s="94"/>
-      <c r="H233" s="95"/>
-      <c r="I233" s="115" t="s">
+      <c r="G233" s="103"/>
+      <c r="H233" s="104"/>
+      <c r="I233" s="116" t="s">
         <v>462</v>
       </c>
-      <c r="J233" s="102"/>
-      <c r="K233" s="102"/>
-      <c r="L233" s="102"/>
-      <c r="M233" s="102"/>
-      <c r="N233" s="102"/>
-      <c r="O233" s="103"/>
-      <c r="P233" s="116" t="s">
+      <c r="J233" s="91"/>
+      <c r="K233" s="91"/>
+      <c r="L233" s="91"/>
+      <c r="M233" s="91"/>
+      <c r="N233" s="91"/>
+      <c r="O233" s="92"/>
+      <c r="P233" s="117" t="s">
         <v>7</v>
       </c>
-      <c r="Q233" s="102"/>
-      <c r="R233" s="103"/>
+      <c r="Q233" s="91"/>
+      <c r="R233" s="92"/>
       <c r="S233" s="16"/>
       <c r="T233" s="16"/>
       <c r="U233" s="16"/>
@@ -51665,36 +52511,36 @@
       <c r="X233" s="16"/>
     </row>
     <row r="234" spans="1:24" ht="20.65">
-      <c r="A234" s="91"/>
-      <c r="B234" s="91"/>
-      <c r="C234" s="91"/>
-      <c r="D234" s="91"/>
-      <c r="E234" s="91"/>
-      <c r="F234" s="96"/>
-      <c r="G234" s="97"/>
-      <c r="H234" s="98"/>
-      <c r="I234" s="117" t="s">
+      <c r="A234" s="98"/>
+      <c r="B234" s="98"/>
+      <c r="C234" s="98"/>
+      <c r="D234" s="98"/>
+      <c r="E234" s="98"/>
+      <c r="F234" s="105"/>
+      <c r="G234" s="106"/>
+      <c r="H234" s="107"/>
+      <c r="I234" s="118" t="s">
         <v>463</v>
       </c>
-      <c r="J234" s="115" t="s">
+      <c r="J234" s="116" t="s">
         <v>9</v>
       </c>
-      <c r="K234" s="103"/>
-      <c r="L234" s="115" t="s">
+      <c r="K234" s="92"/>
+      <c r="L234" s="116" t="s">
         <v>10</v>
       </c>
-      <c r="M234" s="103"/>
-      <c r="N234" s="117" t="s">
+      <c r="M234" s="92"/>
+      <c r="N234" s="118" t="s">
         <v>464</v>
       </c>
-      <c r="O234" s="117" t="s">
+      <c r="O234" s="118" t="s">
         <v>12</v>
       </c>
-      <c r="P234" s="116" t="s">
+      <c r="P234" s="117" t="s">
         <v>465</v>
       </c>
-      <c r="Q234" s="102"/>
-      <c r="R234" s="103"/>
+      <c r="Q234" s="91"/>
+      <c r="R234" s="92"/>
       <c r="S234" s="16"/>
       <c r="T234" s="16"/>
       <c r="U234" s="16"/>
@@ -51703,11 +52549,11 @@
       <c r="X234" s="16"/>
     </row>
     <row r="235" spans="1:24" ht="82.5">
-      <c r="A235" s="112"/>
-      <c r="B235" s="112"/>
-      <c r="C235" s="112"/>
-      <c r="D235" s="112"/>
-      <c r="E235" s="112"/>
+      <c r="A235" s="119"/>
+      <c r="B235" s="119"/>
+      <c r="C235" s="119"/>
+      <c r="D235" s="119"/>
+      <c r="E235" s="119"/>
       <c r="F235" s="52" t="s">
         <v>14</v>
       </c>
@@ -51717,7 +52563,7 @@
       <c r="H235" s="52" t="s">
         <v>16</v>
       </c>
-      <c r="I235" s="112"/>
+      <c r="I235" s="119"/>
       <c r="J235" s="53" t="s">
         <v>15</v>
       </c>
@@ -51730,8 +52576,8 @@
       <c r="M235" s="53" t="s">
         <v>18</v>
       </c>
-      <c r="N235" s="112"/>
-      <c r="O235" s="112"/>
+      <c r="N235" s="119"/>
+      <c r="O235" s="119"/>
       <c r="P235" s="54" t="s">
         <v>466</v>
       </c>
@@ -74841,13 +75687,11 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="A2:A4"/>
-    <mergeCell ref="B2:B4"/>
-    <mergeCell ref="C2:C4"/>
-    <mergeCell ref="D2:D4"/>
-    <mergeCell ref="E2:E4"/>
-    <mergeCell ref="I2:O2"/>
+    <mergeCell ref="A233:A235"/>
+    <mergeCell ref="B233:B235"/>
+    <mergeCell ref="C233:C235"/>
+    <mergeCell ref="D233:D235"/>
+    <mergeCell ref="E233:E235"/>
     <mergeCell ref="P2:R2"/>
     <mergeCell ref="P3:R3"/>
     <mergeCell ref="F233:H234"/>
@@ -74864,11 +75708,13 @@
     <mergeCell ref="J3:K3"/>
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="N3:N4"/>
-    <mergeCell ref="A233:A235"/>
-    <mergeCell ref="B233:B235"/>
-    <mergeCell ref="C233:C235"/>
-    <mergeCell ref="D233:D235"/>
-    <mergeCell ref="E233:E235"/>
+    <mergeCell ref="O3:O4"/>
+    <mergeCell ref="A2:A4"/>
+    <mergeCell ref="B2:B4"/>
+    <mergeCell ref="C2:C4"/>
+    <mergeCell ref="D2:D4"/>
+    <mergeCell ref="E2:E4"/>
+    <mergeCell ref="I2:O2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
